--- a/sample_data/Modele_Mapping_ZS_vierge.xlsx
+++ b/sample_data/Modele_Mapping_ZS_vierge.xlsx
@@ -45,7 +45,7 @@
     <numFmt numFmtId="164" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY HH:MM"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -72,6 +72,10 @@
     </font>
     <font>
       <i val="1"/>
+      <color rgb="005F6B7A"/>
+      <sz val="9"/>
+    </font>
+    <font>
       <color rgb="005F6B7A"/>
       <sz val="9"/>
     </font>
@@ -165,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -180,16 +184,17 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -201,7 +206,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -887,7 +892,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1115,12 +1120,36 @@
         </is>
       </c>
     </row>
+    <row r="23">
+      <c r="B23" s="12" t="inlineStr">
+        <is>
+          <t>Système de gestion de l’incident, SGI-RDC, avec l’appui de UMIE-INRB</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="12" t="inlineStr">
+        <is>
+          <t>Équipe de développement : Onesime Mbulayi et al.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="12" t="inlineStr">
+        <is>
+          <t>Pour tout contact : mbonesime@gmail.com, dav.ebengo@umie-inrb.org</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="B1:C1"/>
-    <mergeCell ref="B3:C3"/>
+  <mergeCells count="7">
+    <mergeCell ref="B24:C24"/>
     <mergeCell ref="B16:C16"/>
     <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B1:C1"/>
   </mergeCells>
   <pageMargins left="0.4" right="0.4" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -92622,7 +92651,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>FICHE DU CAS — MAPPING DU PARCOURS ÉPIDÉMIOLOGIQUE</t>
         </is>
@@ -92631,346 +92660,346 @@
       <c r="C1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Remplir la colonne « Valeur ». Cases jaunes = indispensables. Inconnu : laisser vide (affiché « ? »).</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="14" t="inlineStr">
+      <c r="A3" s="15" t="inlineStr">
         <is>
           <t>Champ</t>
         </is>
       </c>
-      <c r="B3" s="14" t="inlineStr">
+      <c r="B3" s="15" t="inlineStr">
         <is>
           <t>Valeur</t>
         </is>
       </c>
-      <c r="C3" s="14" t="inlineStr">
+      <c r="C3" s="15" t="inlineStr">
         <is>
           <t>Aide</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="15" t="inlineStr">
+      <c r="A4" s="16" t="inlineStr">
         <is>
           <t>IDENTIFICATION DU CAS</t>
         </is>
       </c>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="16" t="inlineStr">
+      <c r="A5" s="17" t="inlineStr">
         <is>
           <t>Rang du cas</t>
         </is>
       </c>
-      <c r="B5" s="17" t="n"/>
-      <c r="C5" s="18" t="inlineStr">
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="19" t="inlineStr">
         <is>
           <t>Numéro d'ordre du cas confirmé dans la ZS (1, 2, 3…)</t>
         </is>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="16" t="inlineStr">
+      <c r="A6" s="17" t="inlineStr">
         <is>
           <t>Maladie</t>
         </is>
       </c>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="18" t="inlineStr">
         <is>
           <t>MVE</t>
         </is>
       </c>
-      <c r="C6" s="18" t="inlineStr">
+      <c r="C6" s="19" t="inlineStr">
         <is>
           <t>Liste : MVE, Marburg, Mpox, Choléra, Rougeole, Autre</t>
         </is>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="19" t="inlineStr">
+      <c r="A7" s="20" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="B7" s="20" t="inlineStr">
+      <c r="B7" s="21" t="inlineStr">
         <is>
           <t>Confirmé</t>
         </is>
       </c>
-      <c r="C7" s="18" t="inlineStr">
+      <c r="C7" s="19" t="inlineStr">
         <is>
           <t>Confirmé / Probable / Suspect</t>
         </is>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="16" t="inlineStr">
+      <c r="A8" s="17" t="inlineStr">
         <is>
           <t>Sexe</t>
         </is>
       </c>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="18" t="inlineStr">
         <is>
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="C8" s="18" t="inlineStr">
+      <c r="C8" s="19" t="inlineStr">
         <is>
           <t>M / F / Inconnu</t>
         </is>
       </c>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="17" t="inlineStr">
         <is>
           <t>Âge</t>
         </is>
       </c>
-      <c r="B9" s="17" t="n"/>
-      <c r="C9" s="18" t="inlineStr">
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="19" t="inlineStr">
         <is>
           <t>Nombre ; vide si inconnu</t>
         </is>
       </c>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="19" t="inlineStr">
+      <c r="A10" s="20" t="inlineStr">
         <is>
           <t>Unité âge</t>
         </is>
       </c>
-      <c r="B10" s="20" t="inlineStr">
+      <c r="B10" s="21" t="inlineStr">
         <is>
           <t>ans</t>
         </is>
       </c>
-      <c r="C10" s="18" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>ans / mois</t>
         </is>
       </c>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="19" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>Profession</t>
         </is>
       </c>
-      <c r="B11" s="20" t="inlineStr"/>
-      <c r="C11" s="18" t="inlineStr"/>
+      <c r="B11" s="21" t="inlineStr"/>
+      <c r="C11" s="19" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="15" t="inlineStr">
+      <c r="A12" s="16" t="inlineStr">
         <is>
           <t>LOCALISATION (pyramide sanitaire RDC)</t>
         </is>
       </c>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="16" t="inlineStr">
+      <c r="A13" s="17" t="inlineStr">
         <is>
           <t>Province</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr"/>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="B13" s="18" t="inlineStr"/>
+      <c r="C13" s="19" t="inlineStr">
         <is>
           <t>Choisir dans la liste</t>
         </is>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="16" t="inlineStr">
+      <c r="A14" s="17" t="inlineStr">
         <is>
           <t>Zone de santé</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr"/>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="B14" s="18" t="inlineStr"/>
+      <c r="C14" s="19" t="inlineStr">
         <is>
           <t>Liste filtrée selon la province</t>
         </is>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="16" t="inlineStr">
+      <c r="A15" s="17" t="inlineStr">
         <is>
           <t>Aire de santé</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr"/>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="B15" s="18" t="inlineStr"/>
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>Liste filtrée selon la ZS ; saisie libre si absente</t>
         </is>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="19" t="inlineStr">
+      <c r="A16" s="20" t="inlineStr">
         <is>
           <t>Village / quartier</t>
         </is>
       </c>
-      <c r="B16" s="20" t="inlineStr"/>
-      <c r="C16" s="18" t="inlineStr"/>
+      <c r="B16" s="21" t="inlineStr"/>
+      <c r="C16" s="19" t="inlineStr"/>
     </row>
     <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="19" t="inlineStr">
+      <c r="A17" s="20" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="B17" s="20" t="n"/>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="B17" s="21" t="n"/>
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>GPS facultatif, ex. 2,6317</t>
         </is>
       </c>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="19" t="inlineStr">
+      <c r="A18" s="20" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
-      <c r="B18" s="20" t="n"/>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="B18" s="21" t="n"/>
+      <c r="C18" s="19" t="inlineStr">
         <is>
           <t>GPS facultatif, ex. 24,3912</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="15" t="inlineStr">
+      <c r="A19" s="16" t="inlineStr">
         <is>
           <t>CLINIQUE ET ISSUE</t>
         </is>
       </c>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="17" t="inlineStr">
         <is>
           <t>Début symptômes</t>
         </is>
       </c>
-      <c r="B20" s="21" t="n"/>
-      <c r="C20" s="18" t="inlineStr">
+      <c r="B20" s="22" t="n"/>
+      <c r="C20" s="19" t="inlineStr">
         <is>
           <t>J0 — JJ/MM/AAAA. Sert au calcul des fenêtres d'exposition</t>
         </is>
       </c>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="19" t="inlineStr">
+      <c r="A21" s="20" t="inlineStr">
         <is>
           <t>Symptômes (séparés par ;)</t>
         </is>
       </c>
-      <c r="B21" s="20" t="inlineStr"/>
-      <c r="C21" s="18" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr"/>
+      <c r="C21" s="19" t="inlineStr">
         <is>
           <t>ex. Fièvre; Céphalées; Méléna</t>
         </is>
       </c>
     </row>
     <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="19" t="inlineStr">
+      <c r="A22" s="20" t="inlineStr">
         <is>
           <t>Autres symptômes</t>
         </is>
       </c>
-      <c r="B22" s="20" t="inlineStr"/>
-      <c r="C22" s="18" t="inlineStr"/>
+      <c r="B22" s="21" t="inlineStr"/>
+      <c r="C22" s="19" t="inlineStr"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="17" t="inlineStr">
         <is>
           <t>Date confirmation</t>
         </is>
       </c>
-      <c r="B23" s="21" t="n"/>
-      <c r="C23" s="18" t="inlineStr">
+      <c r="B23" s="22" t="n"/>
+      <c r="C23" s="19" t="inlineStr">
         <is>
           <t>JJ/MM/AAAA</t>
         </is>
       </c>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="16" t="inlineStr">
+      <c r="A24" s="17" t="inlineStr">
         <is>
           <t>Issue</t>
         </is>
       </c>
-      <c r="B24" s="17" t="inlineStr">
+      <c r="B24" s="18" t="inlineStr">
         <is>
           <t>Inconnu</t>
         </is>
       </c>
-      <c r="C24" s="18" t="inlineStr">
+      <c r="C24" s="19" t="inlineStr">
         <is>
           <t>Vivant / Décès / Guéri / En traitement / Inconnu</t>
         </is>
       </c>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="19" t="inlineStr">
+      <c r="A25" s="20" t="inlineStr">
         <is>
           <t>Date décès</t>
         </is>
       </c>
-      <c r="B25" s="22" t="n"/>
-      <c r="C25" s="18" t="inlineStr">
+      <c r="B25" s="23" t="n"/>
+      <c r="C25" s="19" t="inlineStr">
         <is>
           <t>JJ/MM/AAAA si décès</t>
         </is>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="19" t="inlineStr">
+      <c r="A26" s="20" t="inlineStr">
         <is>
           <t>Risque global (vide = auto)</t>
         </is>
       </c>
-      <c r="B26" s="20" t="inlineStr"/>
-      <c r="C26" s="18" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr"/>
+      <c r="C26" s="19" t="inlineStr">
         <is>
           <t>Laisser vide : l'outil le calcule</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="15" t="inlineStr">
+      <c r="A27" s="16" t="inlineStr">
         <is>
           <t>INVESTIGATION</t>
         </is>
       </c>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
+      <c r="A28" s="17" t="inlineStr">
         <is>
           <t>Investigateur</t>
         </is>
       </c>
-      <c r="B28" s="17" t="inlineStr"/>
-      <c r="C28" s="18" t="inlineStr">
+      <c r="B28" s="18" t="inlineStr"/>
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>Nom / équipe</t>
         </is>
       </c>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="19" t="inlineStr">
+      <c r="A29" s="20" t="inlineStr">
         <is>
           <t>Date investigation</t>
         </is>
       </c>
-      <c r="B29" s="22" t="n"/>
-      <c r="C29" s="18" t="inlineStr">
+      <c r="B29" s="23" t="n"/>
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>JJ/MM/AAAA</t>
         </is>
@@ -93170,7 +93199,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>CHRONOLOGIE DU PARCOURS</t>
         </is>
@@ -93193,858 +93222,858 @@
       <c r="Q1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Une ligne = une étape, dans l'ordre d'affichage. Date inconnue : laisser vide. Risque vide = calcul automatique.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Date début</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Date fin</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Heure</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Heure approx.</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Date incertaine</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>Lieu</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>Lieu d'arrivée</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
+      <c r="H3" s="24" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="I3" s="23" t="inlineStr">
+      <c r="I3" s="24" t="inlineStr">
         <is>
           <t>Titre</t>
         </is>
       </c>
-      <c r="J3" s="23" t="inlineStr">
+      <c r="J3" s="24" t="inlineStr">
         <is>
           <t>Description</t>
         </is>
       </c>
-      <c r="K3" s="23" t="inlineStr">
+      <c r="K3" s="24" t="inlineStr">
         <is>
           <t>Transport</t>
         </is>
       </c>
-      <c r="L3" s="23" t="inlineStr">
+      <c r="L3" s="24" t="inlineStr">
         <is>
           <t>Personnes présentes</t>
         </is>
       </c>
-      <c r="M3" s="23" t="inlineStr">
+      <c r="M3" s="24" t="inlineStr">
         <is>
           <t>Contact corps</t>
         </is>
       </c>
-      <c r="N3" s="23" t="inlineStr">
+      <c r="N3" s="24" t="inlineStr">
         <is>
           <t>Liquides biologiques</t>
         </is>
       </c>
-      <c r="O3" s="23" t="inlineStr">
+      <c r="O3" s="24" t="inlineStr">
         <is>
           <t>Sans PCI</t>
         </is>
       </c>
-      <c r="P3" s="23" t="inlineStr">
+      <c r="P3" s="24" t="inlineStr">
         <is>
           <t>Sécurisé</t>
         </is>
       </c>
-      <c r="Q3" s="23" t="inlineStr">
+      <c r="Q3" s="24" t="inlineStr">
         <is>
           <t>Risque (vide = auto)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="24" t="n"/>
-      <c r="B4" s="24" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="26" t="n"/>
-      <c r="E4" s="26" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="27" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="27" t="n"/>
-      <c r="L4" s="25" t="n"/>
-      <c r="M4" s="26" t="n"/>
-      <c r="N4" s="26" t="n"/>
-      <c r="O4" s="26" t="n"/>
-      <c r="P4" s="26" t="n"/>
-      <c r="Q4" s="27" t="n"/>
+      <c r="A4" s="25" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="26" t="n"/>
+      <c r="G4" s="26" t="n"/>
+      <c r="H4" s="28" t="n"/>
+      <c r="I4" s="26" t="n"/>
+      <c r="J4" s="26" t="n"/>
+      <c r="K4" s="28" t="n"/>
+      <c r="L4" s="26" t="n"/>
+      <c r="M4" s="27" t="n"/>
+      <c r="N4" s="27" t="n"/>
+      <c r="O4" s="27" t="n"/>
+      <c r="P4" s="27" t="n"/>
+      <c r="Q4" s="28" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="28" t="n"/>
-      <c r="B5" s="28" t="n"/>
-      <c r="C5" s="29" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="29" t="n"/>
-      <c r="G5" s="29" t="n"/>
-      <c r="H5" s="31" t="n"/>
-      <c r="I5" s="29" t="n"/>
-      <c r="J5" s="29" t="n"/>
-      <c r="K5" s="31" t="n"/>
-      <c r="L5" s="29" t="n"/>
-      <c r="M5" s="30" t="n"/>
-      <c r="N5" s="30" t="n"/>
-      <c r="O5" s="30" t="n"/>
-      <c r="P5" s="30" t="n"/>
-      <c r="Q5" s="31" t="n"/>
+      <c r="A5" s="29" t="n"/>
+      <c r="B5" s="29" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="30" t="n"/>
+      <c r="G5" s="30" t="n"/>
+      <c r="H5" s="32" t="n"/>
+      <c r="I5" s="30" t="n"/>
+      <c r="J5" s="30" t="n"/>
+      <c r="K5" s="32" t="n"/>
+      <c r="L5" s="30" t="n"/>
+      <c r="M5" s="31" t="n"/>
+      <c r="N5" s="31" t="n"/>
+      <c r="O5" s="31" t="n"/>
+      <c r="P5" s="31" t="n"/>
+      <c r="Q5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="n"/>
-      <c r="B6" s="24" t="n"/>
-      <c r="C6" s="25" t="n"/>
-      <c r="D6" s="26" t="n"/>
-      <c r="E6" s="26" t="n"/>
-      <c r="F6" s="25" t="n"/>
-      <c r="G6" s="25" t="n"/>
-      <c r="H6" s="27" t="n"/>
-      <c r="I6" s="25" t="n"/>
-      <c r="J6" s="25" t="n"/>
-      <c r="K6" s="27" t="n"/>
-      <c r="L6" s="25" t="n"/>
-      <c r="M6" s="26" t="n"/>
-      <c r="N6" s="26" t="n"/>
-      <c r="O6" s="26" t="n"/>
-      <c r="P6" s="26" t="n"/>
-      <c r="Q6" s="27" t="n"/>
+      <c r="A6" s="25" t="n"/>
+      <c r="B6" s="25" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="27" t="n"/>
+      <c r="F6" s="26" t="n"/>
+      <c r="G6" s="26" t="n"/>
+      <c r="H6" s="28" t="n"/>
+      <c r="I6" s="26" t="n"/>
+      <c r="J6" s="26" t="n"/>
+      <c r="K6" s="28" t="n"/>
+      <c r="L6" s="26" t="n"/>
+      <c r="M6" s="27" t="n"/>
+      <c r="N6" s="27" t="n"/>
+      <c r="O6" s="27" t="n"/>
+      <c r="P6" s="27" t="n"/>
+      <c r="Q6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="28" t="n"/>
-      <c r="B7" s="28" t="n"/>
-      <c r="C7" s="29" t="n"/>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="29" t="n"/>
-      <c r="G7" s="29" t="n"/>
-      <c r="H7" s="31" t="n"/>
-      <c r="I7" s="29" t="n"/>
-      <c r="J7" s="29" t="n"/>
-      <c r="K7" s="31" t="n"/>
-      <c r="L7" s="29" t="n"/>
-      <c r="M7" s="30" t="n"/>
-      <c r="N7" s="30" t="n"/>
-      <c r="O7" s="30" t="n"/>
-      <c r="P7" s="30" t="n"/>
-      <c r="Q7" s="31" t="n"/>
+      <c r="A7" s="29" t="n"/>
+      <c r="B7" s="29" t="n"/>
+      <c r="C7" s="30" t="n"/>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="31" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="30" t="n"/>
+      <c r="H7" s="32" t="n"/>
+      <c r="I7" s="30" t="n"/>
+      <c r="J7" s="30" t="n"/>
+      <c r="K7" s="32" t="n"/>
+      <c r="L7" s="30" t="n"/>
+      <c r="M7" s="31" t="n"/>
+      <c r="N7" s="31" t="n"/>
+      <c r="O7" s="31" t="n"/>
+      <c r="P7" s="31" t="n"/>
+      <c r="Q7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="24" t="n"/>
-      <c r="B8" s="24" t="n"/>
-      <c r="C8" s="25" t="n"/>
-      <c r="D8" s="26" t="n"/>
-      <c r="E8" s="26" t="n"/>
-      <c r="F8" s="25" t="n"/>
-      <c r="G8" s="25" t="n"/>
-      <c r="H8" s="27" t="n"/>
-      <c r="I8" s="25" t="n"/>
-      <c r="J8" s="25" t="n"/>
-      <c r="K8" s="27" t="n"/>
-      <c r="L8" s="25" t="n"/>
-      <c r="M8" s="26" t="n"/>
-      <c r="N8" s="26" t="n"/>
-      <c r="O8" s="26" t="n"/>
-      <c r="P8" s="26" t="n"/>
-      <c r="Q8" s="27" t="n"/>
+      <c r="A8" s="25" t="n"/>
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="26" t="n"/>
+      <c r="G8" s="26" t="n"/>
+      <c r="H8" s="28" t="n"/>
+      <c r="I8" s="26" t="n"/>
+      <c r="J8" s="26" t="n"/>
+      <c r="K8" s="28" t="n"/>
+      <c r="L8" s="26" t="n"/>
+      <c r="M8" s="27" t="n"/>
+      <c r="N8" s="27" t="n"/>
+      <c r="O8" s="27" t="n"/>
+      <c r="P8" s="27" t="n"/>
+      <c r="Q8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="28" t="n"/>
-      <c r="B9" s="28" t="n"/>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="30" t="n"/>
-      <c r="F9" s="29" t="n"/>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="31" t="n"/>
-      <c r="I9" s="29" t="n"/>
-      <c r="J9" s="29" t="n"/>
-      <c r="K9" s="31" t="n"/>
-      <c r="L9" s="29" t="n"/>
-      <c r="M9" s="30" t="n"/>
-      <c r="N9" s="30" t="n"/>
-      <c r="O9" s="30" t="n"/>
-      <c r="P9" s="30" t="n"/>
-      <c r="Q9" s="31" t="n"/>
+      <c r="A9" s="29" t="n"/>
+      <c r="B9" s="29" t="n"/>
+      <c r="C9" s="30" t="n"/>
+      <c r="D9" s="31" t="n"/>
+      <c r="E9" s="31" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="30" t="n"/>
+      <c r="H9" s="32" t="n"/>
+      <c r="I9" s="30" t="n"/>
+      <c r="J9" s="30" t="n"/>
+      <c r="K9" s="32" t="n"/>
+      <c r="L9" s="30" t="n"/>
+      <c r="M9" s="31" t="n"/>
+      <c r="N9" s="31" t="n"/>
+      <c r="O9" s="31" t="n"/>
+      <c r="P9" s="31" t="n"/>
+      <c r="Q9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="n"/>
-      <c r="B10" s="24" t="n"/>
-      <c r="C10" s="25" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="25" t="n"/>
-      <c r="G10" s="25" t="n"/>
-      <c r="H10" s="27" t="n"/>
-      <c r="I10" s="25" t="n"/>
-      <c r="J10" s="25" t="n"/>
-      <c r="K10" s="27" t="n"/>
-      <c r="L10" s="25" t="n"/>
-      <c r="M10" s="26" t="n"/>
-      <c r="N10" s="26" t="n"/>
-      <c r="O10" s="26" t="n"/>
-      <c r="P10" s="26" t="n"/>
-      <c r="Q10" s="27" t="n"/>
+      <c r="A10" s="25" t="n"/>
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="26" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="28" t="n"/>
+      <c r="I10" s="26" t="n"/>
+      <c r="J10" s="26" t="n"/>
+      <c r="K10" s="28" t="n"/>
+      <c r="L10" s="26" t="n"/>
+      <c r="M10" s="27" t="n"/>
+      <c r="N10" s="27" t="n"/>
+      <c r="O10" s="27" t="n"/>
+      <c r="P10" s="27" t="n"/>
+      <c r="Q10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="28" t="n"/>
-      <c r="B11" s="28" t="n"/>
-      <c r="C11" s="29" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="29" t="n"/>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="31" t="n"/>
-      <c r="I11" s="29" t="n"/>
-      <c r="J11" s="29" t="n"/>
-      <c r="K11" s="31" t="n"/>
-      <c r="L11" s="29" t="n"/>
-      <c r="M11" s="30" t="n"/>
-      <c r="N11" s="30" t="n"/>
-      <c r="O11" s="30" t="n"/>
-      <c r="P11" s="30" t="n"/>
-      <c r="Q11" s="31" t="n"/>
+      <c r="A11" s="29" t="n"/>
+      <c r="B11" s="29" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="30" t="n"/>
+      <c r="H11" s="32" t="n"/>
+      <c r="I11" s="30" t="n"/>
+      <c r="J11" s="30" t="n"/>
+      <c r="K11" s="32" t="n"/>
+      <c r="L11" s="30" t="n"/>
+      <c r="M11" s="31" t="n"/>
+      <c r="N11" s="31" t="n"/>
+      <c r="O11" s="31" t="n"/>
+      <c r="P11" s="31" t="n"/>
+      <c r="Q11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="n"/>
-      <c r="B12" s="24" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="25" t="n"/>
-      <c r="H12" s="27" t="n"/>
-      <c r="I12" s="25" t="n"/>
-      <c r="J12" s="25" t="n"/>
-      <c r="K12" s="27" t="n"/>
-      <c r="L12" s="25" t="n"/>
-      <c r="M12" s="26" t="n"/>
-      <c r="N12" s="26" t="n"/>
-      <c r="O12" s="26" t="n"/>
-      <c r="P12" s="26" t="n"/>
-      <c r="Q12" s="27" t="n"/>
+      <c r="A12" s="25" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="26" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="28" t="n"/>
+      <c r="I12" s="26" t="n"/>
+      <c r="J12" s="26" t="n"/>
+      <c r="K12" s="28" t="n"/>
+      <c r="L12" s="26" t="n"/>
+      <c r="M12" s="27" t="n"/>
+      <c r="N12" s="27" t="n"/>
+      <c r="O12" s="27" t="n"/>
+      <c r="P12" s="27" t="n"/>
+      <c r="Q12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="28" t="n"/>
-      <c r="B13" s="28" t="n"/>
-      <c r="C13" s="29" t="n"/>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="30" t="n"/>
-      <c r="F13" s="29" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="31" t="n"/>
-      <c r="I13" s="29" t="n"/>
-      <c r="J13" s="29" t="n"/>
-      <c r="K13" s="31" t="n"/>
-      <c r="L13" s="29" t="n"/>
-      <c r="M13" s="30" t="n"/>
-      <c r="N13" s="30" t="n"/>
-      <c r="O13" s="30" t="n"/>
-      <c r="P13" s="30" t="n"/>
-      <c r="Q13" s="31" t="n"/>
+      <c r="A13" s="29" t="n"/>
+      <c r="B13" s="29" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="30" t="n"/>
+      <c r="H13" s="32" t="n"/>
+      <c r="I13" s="30" t="n"/>
+      <c r="J13" s="30" t="n"/>
+      <c r="K13" s="32" t="n"/>
+      <c r="L13" s="30" t="n"/>
+      <c r="M13" s="31" t="n"/>
+      <c r="N13" s="31" t="n"/>
+      <c r="O13" s="31" t="n"/>
+      <c r="P13" s="31" t="n"/>
+      <c r="Q13" s="32" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="24" t="n"/>
-      <c r="B14" s="24" t="n"/>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="27" t="n"/>
-      <c r="I14" s="25" t="n"/>
-      <c r="J14" s="25" t="n"/>
-      <c r="K14" s="27" t="n"/>
-      <c r="L14" s="25" t="n"/>
-      <c r="M14" s="26" t="n"/>
-      <c r="N14" s="26" t="n"/>
-      <c r="O14" s="26" t="n"/>
-      <c r="P14" s="26" t="n"/>
-      <c r="Q14" s="27" t="n"/>
+      <c r="A14" s="25" t="n"/>
+      <c r="B14" s="25" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="26" t="n"/>
+      <c r="G14" s="26" t="n"/>
+      <c r="H14" s="28" t="n"/>
+      <c r="I14" s="26" t="n"/>
+      <c r="J14" s="26" t="n"/>
+      <c r="K14" s="28" t="n"/>
+      <c r="L14" s="26" t="n"/>
+      <c r="M14" s="27" t="n"/>
+      <c r="N14" s="27" t="n"/>
+      <c r="O14" s="27" t="n"/>
+      <c r="P14" s="27" t="n"/>
+      <c r="Q14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="28" t="n"/>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="29" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="31" t="n"/>
-      <c r="I15" s="29" t="n"/>
-      <c r="J15" s="29" t="n"/>
-      <c r="K15" s="31" t="n"/>
-      <c r="L15" s="29" t="n"/>
-      <c r="M15" s="30" t="n"/>
-      <c r="N15" s="30" t="n"/>
-      <c r="O15" s="30" t="n"/>
-      <c r="P15" s="30" t="n"/>
-      <c r="Q15" s="31" t="n"/>
+      <c r="A15" s="29" t="n"/>
+      <c r="B15" s="29" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="30" t="n"/>
+      <c r="H15" s="32" t="n"/>
+      <c r="I15" s="30" t="n"/>
+      <c r="J15" s="30" t="n"/>
+      <c r="K15" s="32" t="n"/>
+      <c r="L15" s="30" t="n"/>
+      <c r="M15" s="31" t="n"/>
+      <c r="N15" s="31" t="n"/>
+      <c r="O15" s="31" t="n"/>
+      <c r="P15" s="31" t="n"/>
+      <c r="Q15" s="32" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="n"/>
-      <c r="B16" s="24" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="25" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="27" t="n"/>
-      <c r="I16" s="25" t="n"/>
-      <c r="J16" s="25" t="n"/>
-      <c r="K16" s="27" t="n"/>
-      <c r="L16" s="25" t="n"/>
-      <c r="M16" s="26" t="n"/>
-      <c r="N16" s="26" t="n"/>
-      <c r="O16" s="26" t="n"/>
-      <c r="P16" s="26" t="n"/>
-      <c r="Q16" s="27" t="n"/>
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="26" t="n"/>
+      <c r="G16" s="26" t="n"/>
+      <c r="H16" s="28" t="n"/>
+      <c r="I16" s="26" t="n"/>
+      <c r="J16" s="26" t="n"/>
+      <c r="K16" s="28" t="n"/>
+      <c r="L16" s="26" t="n"/>
+      <c r="M16" s="27" t="n"/>
+      <c r="N16" s="27" t="n"/>
+      <c r="O16" s="27" t="n"/>
+      <c r="P16" s="27" t="n"/>
+      <c r="Q16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="28" t="n"/>
-      <c r="B17" s="28" t="n"/>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="29" t="n"/>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="31" t="n"/>
-      <c r="I17" s="29" t="n"/>
-      <c r="J17" s="29" t="n"/>
-      <c r="K17" s="31" t="n"/>
-      <c r="L17" s="29" t="n"/>
-      <c r="M17" s="30" t="n"/>
-      <c r="N17" s="30" t="n"/>
-      <c r="O17" s="30" t="n"/>
-      <c r="P17" s="30" t="n"/>
-      <c r="Q17" s="31" t="n"/>
+      <c r="A17" s="29" t="n"/>
+      <c r="B17" s="29" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="30" t="n"/>
+      <c r="H17" s="32" t="n"/>
+      <c r="I17" s="30" t="n"/>
+      <c r="J17" s="30" t="n"/>
+      <c r="K17" s="32" t="n"/>
+      <c r="L17" s="30" t="n"/>
+      <c r="M17" s="31" t="n"/>
+      <c r="N17" s="31" t="n"/>
+      <c r="O17" s="31" t="n"/>
+      <c r="P17" s="31" t="n"/>
+      <c r="Q17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="n"/>
-      <c r="B18" s="24" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="25" t="n"/>
-      <c r="G18" s="25" t="n"/>
-      <c r="H18" s="27" t="n"/>
-      <c r="I18" s="25" t="n"/>
-      <c r="J18" s="25" t="n"/>
-      <c r="K18" s="27" t="n"/>
-      <c r="L18" s="25" t="n"/>
-      <c r="M18" s="26" t="n"/>
-      <c r="N18" s="26" t="n"/>
-      <c r="O18" s="26" t="n"/>
-      <c r="P18" s="26" t="n"/>
-      <c r="Q18" s="27" t="n"/>
+      <c r="A18" s="25" t="n"/>
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="26" t="n"/>
+      <c r="G18" s="26" t="n"/>
+      <c r="H18" s="28" t="n"/>
+      <c r="I18" s="26" t="n"/>
+      <c r="J18" s="26" t="n"/>
+      <c r="K18" s="28" t="n"/>
+      <c r="L18" s="26" t="n"/>
+      <c r="M18" s="27" t="n"/>
+      <c r="N18" s="27" t="n"/>
+      <c r="O18" s="27" t="n"/>
+      <c r="P18" s="27" t="n"/>
+      <c r="Q18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="28" t="n"/>
-      <c r="B19" s="28" t="n"/>
-      <c r="C19" s="29" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="29" t="n"/>
-      <c r="G19" s="29" t="n"/>
-      <c r="H19" s="31" t="n"/>
-      <c r="I19" s="29" t="n"/>
-      <c r="J19" s="29" t="n"/>
-      <c r="K19" s="31" t="n"/>
-      <c r="L19" s="29" t="n"/>
-      <c r="M19" s="30" t="n"/>
-      <c r="N19" s="30" t="n"/>
-      <c r="O19" s="30" t="n"/>
-      <c r="P19" s="30" t="n"/>
-      <c r="Q19" s="31" t="n"/>
+      <c r="A19" s="29" t="n"/>
+      <c r="B19" s="29" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="30" t="n"/>
+      <c r="H19" s="32" t="n"/>
+      <c r="I19" s="30" t="n"/>
+      <c r="J19" s="30" t="n"/>
+      <c r="K19" s="32" t="n"/>
+      <c r="L19" s="30" t="n"/>
+      <c r="M19" s="31" t="n"/>
+      <c r="N19" s="31" t="n"/>
+      <c r="O19" s="31" t="n"/>
+      <c r="P19" s="31" t="n"/>
+      <c r="Q19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="n"/>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="25" t="n"/>
-      <c r="G20" s="25" t="n"/>
-      <c r="H20" s="27" t="n"/>
-      <c r="I20" s="25" t="n"/>
-      <c r="J20" s="25" t="n"/>
-      <c r="K20" s="27" t="n"/>
-      <c r="L20" s="25" t="n"/>
-      <c r="M20" s="26" t="n"/>
-      <c r="N20" s="26" t="n"/>
-      <c r="O20" s="26" t="n"/>
-      <c r="P20" s="26" t="n"/>
-      <c r="Q20" s="27" t="n"/>
+      <c r="A20" s="25" t="n"/>
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="26" t="n"/>
+      <c r="G20" s="26" t="n"/>
+      <c r="H20" s="28" t="n"/>
+      <c r="I20" s="26" t="n"/>
+      <c r="J20" s="26" t="n"/>
+      <c r="K20" s="28" t="n"/>
+      <c r="L20" s="26" t="n"/>
+      <c r="M20" s="27" t="n"/>
+      <c r="N20" s="27" t="n"/>
+      <c r="O20" s="27" t="n"/>
+      <c r="P20" s="27" t="n"/>
+      <c r="Q20" s="28" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="28" t="n"/>
-      <c r="B21" s="28" t="n"/>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="29" t="n"/>
-      <c r="G21" s="29" t="n"/>
-      <c r="H21" s="31" t="n"/>
-      <c r="I21" s="29" t="n"/>
-      <c r="J21" s="29" t="n"/>
-      <c r="K21" s="31" t="n"/>
-      <c r="L21" s="29" t="n"/>
-      <c r="M21" s="30" t="n"/>
-      <c r="N21" s="30" t="n"/>
-      <c r="O21" s="30" t="n"/>
-      <c r="P21" s="30" t="n"/>
-      <c r="Q21" s="31" t="n"/>
+      <c r="A21" s="29" t="n"/>
+      <c r="B21" s="29" t="n"/>
+      <c r="C21" s="30" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="30" t="n"/>
+      <c r="H21" s="32" t="n"/>
+      <c r="I21" s="30" t="n"/>
+      <c r="J21" s="30" t="n"/>
+      <c r="K21" s="32" t="n"/>
+      <c r="L21" s="30" t="n"/>
+      <c r="M21" s="31" t="n"/>
+      <c r="N21" s="31" t="n"/>
+      <c r="O21" s="31" t="n"/>
+      <c r="P21" s="31" t="n"/>
+      <c r="Q21" s="32" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="24" t="n"/>
-      <c r="B22" s="24" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="25" t="n"/>
-      <c r="G22" s="25" t="n"/>
-      <c r="H22" s="27" t="n"/>
-      <c r="I22" s="25" t="n"/>
-      <c r="J22" s="25" t="n"/>
-      <c r="K22" s="27" t="n"/>
-      <c r="L22" s="25" t="n"/>
-      <c r="M22" s="26" t="n"/>
-      <c r="N22" s="26" t="n"/>
-      <c r="O22" s="26" t="n"/>
-      <c r="P22" s="26" t="n"/>
-      <c r="Q22" s="27" t="n"/>
+      <c r="A22" s="25" t="n"/>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="26" t="n"/>
+      <c r="G22" s="26" t="n"/>
+      <c r="H22" s="28" t="n"/>
+      <c r="I22" s="26" t="n"/>
+      <c r="J22" s="26" t="n"/>
+      <c r="K22" s="28" t="n"/>
+      <c r="L22" s="26" t="n"/>
+      <c r="M22" s="27" t="n"/>
+      <c r="N22" s="27" t="n"/>
+      <c r="O22" s="27" t="n"/>
+      <c r="P22" s="27" t="n"/>
+      <c r="Q22" s="28" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="28" t="n"/>
-      <c r="B23" s="28" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="29" t="n"/>
-      <c r="G23" s="29" t="n"/>
-      <c r="H23" s="31" t="n"/>
-      <c r="I23" s="29" t="n"/>
-      <c r="J23" s="29" t="n"/>
-      <c r="K23" s="31" t="n"/>
-      <c r="L23" s="29" t="n"/>
-      <c r="M23" s="30" t="n"/>
-      <c r="N23" s="30" t="n"/>
-      <c r="O23" s="30" t="n"/>
-      <c r="P23" s="30" t="n"/>
-      <c r="Q23" s="31" t="n"/>
+      <c r="A23" s="29" t="n"/>
+      <c r="B23" s="29" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="30" t="n"/>
+      <c r="H23" s="32" t="n"/>
+      <c r="I23" s="30" t="n"/>
+      <c r="J23" s="30" t="n"/>
+      <c r="K23" s="32" t="n"/>
+      <c r="L23" s="30" t="n"/>
+      <c r="M23" s="31" t="n"/>
+      <c r="N23" s="31" t="n"/>
+      <c r="O23" s="31" t="n"/>
+      <c r="P23" s="31" t="n"/>
+      <c r="Q23" s="32" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="n"/>
-      <c r="B24" s="24" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="25" t="n"/>
-      <c r="G24" s="25" t="n"/>
-      <c r="H24" s="27" t="n"/>
-      <c r="I24" s="25" t="n"/>
-      <c r="J24" s="25" t="n"/>
-      <c r="K24" s="27" t="n"/>
-      <c r="L24" s="25" t="n"/>
-      <c r="M24" s="26" t="n"/>
-      <c r="N24" s="26" t="n"/>
-      <c r="O24" s="26" t="n"/>
-      <c r="P24" s="26" t="n"/>
-      <c r="Q24" s="27" t="n"/>
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="26" t="n"/>
+      <c r="G24" s="26" t="n"/>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="26" t="n"/>
+      <c r="J24" s="26" t="n"/>
+      <c r="K24" s="28" t="n"/>
+      <c r="L24" s="26" t="n"/>
+      <c r="M24" s="27" t="n"/>
+      <c r="N24" s="27" t="n"/>
+      <c r="O24" s="27" t="n"/>
+      <c r="P24" s="27" t="n"/>
+      <c r="Q24" s="28" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="28" t="n"/>
-      <c r="B25" s="28" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="29" t="n"/>
-      <c r="G25" s="29" t="n"/>
-      <c r="H25" s="31" t="n"/>
-      <c r="I25" s="29" t="n"/>
-      <c r="J25" s="29" t="n"/>
-      <c r="K25" s="31" t="n"/>
-      <c r="L25" s="29" t="n"/>
-      <c r="M25" s="30" t="n"/>
-      <c r="N25" s="30" t="n"/>
-      <c r="O25" s="30" t="n"/>
-      <c r="P25" s="30" t="n"/>
-      <c r="Q25" s="31" t="n"/>
+      <c r="A25" s="29" t="n"/>
+      <c r="B25" s="29" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="30" t="n"/>
+      <c r="H25" s="32" t="n"/>
+      <c r="I25" s="30" t="n"/>
+      <c r="J25" s="30" t="n"/>
+      <c r="K25" s="32" t="n"/>
+      <c r="L25" s="30" t="n"/>
+      <c r="M25" s="31" t="n"/>
+      <c r="N25" s="31" t="n"/>
+      <c r="O25" s="31" t="n"/>
+      <c r="P25" s="31" t="n"/>
+      <c r="Q25" s="32" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="n"/>
-      <c r="B26" s="24" t="n"/>
-      <c r="C26" s="25" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="25" t="n"/>
-      <c r="G26" s="25" t="n"/>
-      <c r="H26" s="27" t="n"/>
-      <c r="I26" s="25" t="n"/>
-      <c r="J26" s="25" t="n"/>
-      <c r="K26" s="27" t="n"/>
-      <c r="L26" s="25" t="n"/>
-      <c r="M26" s="26" t="n"/>
-      <c r="N26" s="26" t="n"/>
-      <c r="O26" s="26" t="n"/>
-      <c r="P26" s="26" t="n"/>
-      <c r="Q26" s="27" t="n"/>
+      <c r="A26" s="25" t="n"/>
+      <c r="B26" s="25" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="26" t="n"/>
+      <c r="G26" s="26" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="26" t="n"/>
+      <c r="J26" s="26" t="n"/>
+      <c r="K26" s="28" t="n"/>
+      <c r="L26" s="26" t="n"/>
+      <c r="M26" s="27" t="n"/>
+      <c r="N26" s="27" t="n"/>
+      <c r="O26" s="27" t="n"/>
+      <c r="P26" s="27" t="n"/>
+      <c r="Q26" s="28" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="28" t="n"/>
-      <c r="B27" s="28" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="29" t="n"/>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="31" t="n"/>
-      <c r="I27" s="29" t="n"/>
-      <c r="J27" s="29" t="n"/>
-      <c r="K27" s="31" t="n"/>
-      <c r="L27" s="29" t="n"/>
-      <c r="M27" s="30" t="n"/>
-      <c r="N27" s="30" t="n"/>
-      <c r="O27" s="30" t="n"/>
-      <c r="P27" s="30" t="n"/>
-      <c r="Q27" s="31" t="n"/>
+      <c r="A27" s="29" t="n"/>
+      <c r="B27" s="29" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="30" t="n"/>
+      <c r="H27" s="32" t="n"/>
+      <c r="I27" s="30" t="n"/>
+      <c r="J27" s="30" t="n"/>
+      <c r="K27" s="32" t="n"/>
+      <c r="L27" s="30" t="n"/>
+      <c r="M27" s="31" t="n"/>
+      <c r="N27" s="31" t="n"/>
+      <c r="O27" s="31" t="n"/>
+      <c r="P27" s="31" t="n"/>
+      <c r="Q27" s="32" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="24" t="n"/>
-      <c r="B28" s="24" t="n"/>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="25" t="n"/>
-      <c r="G28" s="25" t="n"/>
-      <c r="H28" s="27" t="n"/>
-      <c r="I28" s="25" t="n"/>
-      <c r="J28" s="25" t="n"/>
-      <c r="K28" s="27" t="n"/>
-      <c r="L28" s="25" t="n"/>
-      <c r="M28" s="26" t="n"/>
-      <c r="N28" s="26" t="n"/>
-      <c r="O28" s="26" t="n"/>
-      <c r="P28" s="26" t="n"/>
-      <c r="Q28" s="27" t="n"/>
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="26" t="n"/>
+      <c r="G28" s="26" t="n"/>
+      <c r="H28" s="28" t="n"/>
+      <c r="I28" s="26" t="n"/>
+      <c r="J28" s="26" t="n"/>
+      <c r="K28" s="28" t="n"/>
+      <c r="L28" s="26" t="n"/>
+      <c r="M28" s="27" t="n"/>
+      <c r="N28" s="27" t="n"/>
+      <c r="O28" s="27" t="n"/>
+      <c r="P28" s="27" t="n"/>
+      <c r="Q28" s="28" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="28" t="n"/>
-      <c r="B29" s="28" t="n"/>
-      <c r="C29" s="29" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="29" t="n"/>
-      <c r="G29" s="29" t="n"/>
-      <c r="H29" s="31" t="n"/>
-      <c r="I29" s="29" t="n"/>
-      <c r="J29" s="29" t="n"/>
-      <c r="K29" s="31" t="n"/>
-      <c r="L29" s="29" t="n"/>
-      <c r="M29" s="30" t="n"/>
-      <c r="N29" s="30" t="n"/>
-      <c r="O29" s="30" t="n"/>
-      <c r="P29" s="30" t="n"/>
-      <c r="Q29" s="31" t="n"/>
+      <c r="A29" s="29" t="n"/>
+      <c r="B29" s="29" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="30" t="n"/>
+      <c r="H29" s="32" t="n"/>
+      <c r="I29" s="30" t="n"/>
+      <c r="J29" s="30" t="n"/>
+      <c r="K29" s="32" t="n"/>
+      <c r="L29" s="30" t="n"/>
+      <c r="M29" s="31" t="n"/>
+      <c r="N29" s="31" t="n"/>
+      <c r="O29" s="31" t="n"/>
+      <c r="P29" s="31" t="n"/>
+      <c r="Q29" s="32" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="24" t="n"/>
-      <c r="B30" s="24" t="n"/>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="25" t="n"/>
-      <c r="G30" s="25" t="n"/>
-      <c r="H30" s="27" t="n"/>
-      <c r="I30" s="25" t="n"/>
-      <c r="J30" s="25" t="n"/>
-      <c r="K30" s="27" t="n"/>
-      <c r="L30" s="25" t="n"/>
-      <c r="M30" s="26" t="n"/>
-      <c r="N30" s="26" t="n"/>
-      <c r="O30" s="26" t="n"/>
-      <c r="P30" s="26" t="n"/>
-      <c r="Q30" s="27" t="n"/>
+      <c r="A30" s="25" t="n"/>
+      <c r="B30" s="25" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="26" t="n"/>
+      <c r="G30" s="26" t="n"/>
+      <c r="H30" s="28" t="n"/>
+      <c r="I30" s="26" t="n"/>
+      <c r="J30" s="26" t="n"/>
+      <c r="K30" s="28" t="n"/>
+      <c r="L30" s="26" t="n"/>
+      <c r="M30" s="27" t="n"/>
+      <c r="N30" s="27" t="n"/>
+      <c r="O30" s="27" t="n"/>
+      <c r="P30" s="27" t="n"/>
+      <c r="Q30" s="28" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="28" t="n"/>
-      <c r="B31" s="28" t="n"/>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="30" t="n"/>
-      <c r="F31" s="29" t="n"/>
-      <c r="G31" s="29" t="n"/>
-      <c r="H31" s="31" t="n"/>
-      <c r="I31" s="29" t="n"/>
-      <c r="J31" s="29" t="n"/>
-      <c r="K31" s="31" t="n"/>
-      <c r="L31" s="29" t="n"/>
-      <c r="M31" s="30" t="n"/>
-      <c r="N31" s="30" t="n"/>
-      <c r="O31" s="30" t="n"/>
-      <c r="P31" s="30" t="n"/>
-      <c r="Q31" s="31" t="n"/>
+      <c r="A31" s="29" t="n"/>
+      <c r="B31" s="29" t="n"/>
+      <c r="C31" s="30" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="31" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="30" t="n"/>
+      <c r="H31" s="32" t="n"/>
+      <c r="I31" s="30" t="n"/>
+      <c r="J31" s="30" t="n"/>
+      <c r="K31" s="32" t="n"/>
+      <c r="L31" s="30" t="n"/>
+      <c r="M31" s="31" t="n"/>
+      <c r="N31" s="31" t="n"/>
+      <c r="O31" s="31" t="n"/>
+      <c r="P31" s="31" t="n"/>
+      <c r="Q31" s="32" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="24" t="n"/>
-      <c r="B32" s="24" t="n"/>
-      <c r="C32" s="25" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="25" t="n"/>
-      <c r="G32" s="25" t="n"/>
-      <c r="H32" s="27" t="n"/>
-      <c r="I32" s="25" t="n"/>
-      <c r="J32" s="25" t="n"/>
-      <c r="K32" s="27" t="n"/>
-      <c r="L32" s="25" t="n"/>
-      <c r="M32" s="26" t="n"/>
-      <c r="N32" s="26" t="n"/>
-      <c r="O32" s="26" t="n"/>
-      <c r="P32" s="26" t="n"/>
-      <c r="Q32" s="27" t="n"/>
+      <c r="A32" s="25" t="n"/>
+      <c r="B32" s="25" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="27" t="n"/>
+      <c r="F32" s="26" t="n"/>
+      <c r="G32" s="26" t="n"/>
+      <c r="H32" s="28" t="n"/>
+      <c r="I32" s="26" t="n"/>
+      <c r="J32" s="26" t="n"/>
+      <c r="K32" s="28" t="n"/>
+      <c r="L32" s="26" t="n"/>
+      <c r="M32" s="27" t="n"/>
+      <c r="N32" s="27" t="n"/>
+      <c r="O32" s="27" t="n"/>
+      <c r="P32" s="27" t="n"/>
+      <c r="Q32" s="28" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="28" t="n"/>
-      <c r="B33" s="28" t="n"/>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="30" t="n"/>
-      <c r="F33" s="29" t="n"/>
-      <c r="G33" s="29" t="n"/>
-      <c r="H33" s="31" t="n"/>
-      <c r="I33" s="29" t="n"/>
-      <c r="J33" s="29" t="n"/>
-      <c r="K33" s="31" t="n"/>
-      <c r="L33" s="29" t="n"/>
-      <c r="M33" s="30" t="n"/>
-      <c r="N33" s="30" t="n"/>
-      <c r="O33" s="30" t="n"/>
-      <c r="P33" s="30" t="n"/>
-      <c r="Q33" s="31" t="n"/>
+      <c r="A33" s="29" t="n"/>
+      <c r="B33" s="29" t="n"/>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="31" t="n"/>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="30" t="n"/>
+      <c r="H33" s="32" t="n"/>
+      <c r="I33" s="30" t="n"/>
+      <c r="J33" s="30" t="n"/>
+      <c r="K33" s="32" t="n"/>
+      <c r="L33" s="30" t="n"/>
+      <c r="M33" s="31" t="n"/>
+      <c r="N33" s="31" t="n"/>
+      <c r="O33" s="31" t="n"/>
+      <c r="P33" s="31" t="n"/>
+      <c r="Q33" s="32" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="24" t="n"/>
-      <c r="B34" s="24" t="n"/>
-      <c r="C34" s="25" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="25" t="n"/>
-      <c r="G34" s="25" t="n"/>
-      <c r="H34" s="27" t="n"/>
-      <c r="I34" s="25" t="n"/>
-      <c r="J34" s="25" t="n"/>
-      <c r="K34" s="27" t="n"/>
-      <c r="L34" s="25" t="n"/>
-      <c r="M34" s="26" t="n"/>
-      <c r="N34" s="26" t="n"/>
-      <c r="O34" s="26" t="n"/>
-      <c r="P34" s="26" t="n"/>
-      <c r="Q34" s="27" t="n"/>
+      <c r="A34" s="25" t="n"/>
+      <c r="B34" s="25" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="26" t="n"/>
+      <c r="G34" s="26" t="n"/>
+      <c r="H34" s="28" t="n"/>
+      <c r="I34" s="26" t="n"/>
+      <c r="J34" s="26" t="n"/>
+      <c r="K34" s="28" t="n"/>
+      <c r="L34" s="26" t="n"/>
+      <c r="M34" s="27" t="n"/>
+      <c r="N34" s="27" t="n"/>
+      <c r="O34" s="27" t="n"/>
+      <c r="P34" s="27" t="n"/>
+      <c r="Q34" s="28" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="28" t="n"/>
-      <c r="B35" s="28" t="n"/>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="30" t="n"/>
-      <c r="F35" s="29" t="n"/>
-      <c r="G35" s="29" t="n"/>
-      <c r="H35" s="31" t="n"/>
-      <c r="I35" s="29" t="n"/>
-      <c r="J35" s="29" t="n"/>
-      <c r="K35" s="31" t="n"/>
-      <c r="L35" s="29" t="n"/>
-      <c r="M35" s="30" t="n"/>
-      <c r="N35" s="30" t="n"/>
-      <c r="O35" s="30" t="n"/>
-      <c r="P35" s="30" t="n"/>
-      <c r="Q35" s="31" t="n"/>
+      <c r="A35" s="29" t="n"/>
+      <c r="B35" s="29" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="30" t="n"/>
+      <c r="H35" s="32" t="n"/>
+      <c r="I35" s="30" t="n"/>
+      <c r="J35" s="30" t="n"/>
+      <c r="K35" s="32" t="n"/>
+      <c r="L35" s="30" t="n"/>
+      <c r="M35" s="31" t="n"/>
+      <c r="N35" s="31" t="n"/>
+      <c r="O35" s="31" t="n"/>
+      <c r="P35" s="31" t="n"/>
+      <c r="Q35" s="32" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="24" t="n"/>
-      <c r="B36" s="24" t="n"/>
-      <c r="C36" s="25" t="n"/>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="25" t="n"/>
-      <c r="G36" s="25" t="n"/>
-      <c r="H36" s="27" t="n"/>
-      <c r="I36" s="25" t="n"/>
-      <c r="J36" s="25" t="n"/>
-      <c r="K36" s="27" t="n"/>
-      <c r="L36" s="25" t="n"/>
-      <c r="M36" s="26" t="n"/>
-      <c r="N36" s="26" t="n"/>
-      <c r="O36" s="26" t="n"/>
-      <c r="P36" s="26" t="n"/>
-      <c r="Q36" s="27" t="n"/>
+      <c r="A36" s="25" t="n"/>
+      <c r="B36" s="25" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="26" t="n"/>
+      <c r="G36" s="26" t="n"/>
+      <c r="H36" s="28" t="n"/>
+      <c r="I36" s="26" t="n"/>
+      <c r="J36" s="26" t="n"/>
+      <c r="K36" s="28" t="n"/>
+      <c r="L36" s="26" t="n"/>
+      <c r="M36" s="27" t="n"/>
+      <c r="N36" s="27" t="n"/>
+      <c r="O36" s="27" t="n"/>
+      <c r="P36" s="27" t="n"/>
+      <c r="Q36" s="28" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="28" t="n"/>
-      <c r="B37" s="28" t="n"/>
-      <c r="C37" s="29" t="n"/>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="30" t="n"/>
-      <c r="F37" s="29" t="n"/>
-      <c r="G37" s="29" t="n"/>
-      <c r="H37" s="31" t="n"/>
-      <c r="I37" s="29" t="n"/>
-      <c r="J37" s="29" t="n"/>
-      <c r="K37" s="31" t="n"/>
-      <c r="L37" s="29" t="n"/>
-      <c r="M37" s="30" t="n"/>
-      <c r="N37" s="30" t="n"/>
-      <c r="O37" s="30" t="n"/>
-      <c r="P37" s="30" t="n"/>
-      <c r="Q37" s="31" t="n"/>
+      <c r="A37" s="29" t="n"/>
+      <c r="B37" s="29" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="30" t="n"/>
+      <c r="G37" s="30" t="n"/>
+      <c r="H37" s="32" t="n"/>
+      <c r="I37" s="30" t="n"/>
+      <c r="J37" s="30" t="n"/>
+      <c r="K37" s="32" t="n"/>
+      <c r="L37" s="30" t="n"/>
+      <c r="M37" s="31" t="n"/>
+      <c r="N37" s="31" t="n"/>
+      <c r="O37" s="31" t="n"/>
+      <c r="P37" s="31" t="n"/>
+      <c r="Q37" s="32" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="24" t="n"/>
-      <c r="B38" s="24" t="n"/>
-      <c r="C38" s="25" t="n"/>
-      <c r="D38" s="26" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="25" t="n"/>
-      <c r="G38" s="25" t="n"/>
-      <c r="H38" s="27" t="n"/>
-      <c r="I38" s="25" t="n"/>
-      <c r="J38" s="25" t="n"/>
-      <c r="K38" s="27" t="n"/>
-      <c r="L38" s="25" t="n"/>
-      <c r="M38" s="26" t="n"/>
-      <c r="N38" s="26" t="n"/>
-      <c r="O38" s="26" t="n"/>
-      <c r="P38" s="26" t="n"/>
-      <c r="Q38" s="27" t="n"/>
+      <c r="A38" s="25" t="n"/>
+      <c r="B38" s="25" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="26" t="n"/>
+      <c r="G38" s="26" t="n"/>
+      <c r="H38" s="28" t="n"/>
+      <c r="I38" s="26" t="n"/>
+      <c r="J38" s="26" t="n"/>
+      <c r="K38" s="28" t="n"/>
+      <c r="L38" s="26" t="n"/>
+      <c r="M38" s="27" t="n"/>
+      <c r="N38" s="27" t="n"/>
+      <c r="O38" s="27" t="n"/>
+      <c r="P38" s="27" t="n"/>
+      <c r="Q38" s="28" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="28" t="n"/>
-      <c r="B39" s="28" t="n"/>
-      <c r="C39" s="29" t="n"/>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="30" t="n"/>
-      <c r="F39" s="29" t="n"/>
-      <c r="G39" s="29" t="n"/>
-      <c r="H39" s="31" t="n"/>
-      <c r="I39" s="29" t="n"/>
-      <c r="J39" s="29" t="n"/>
-      <c r="K39" s="31" t="n"/>
-      <c r="L39" s="29" t="n"/>
-      <c r="M39" s="30" t="n"/>
-      <c r="N39" s="30" t="n"/>
-      <c r="O39" s="30" t="n"/>
-      <c r="P39" s="30" t="n"/>
-      <c r="Q39" s="31" t="n"/>
+      <c r="A39" s="29" t="n"/>
+      <c r="B39" s="29" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="31" t="n"/>
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="30" t="n"/>
+      <c r="H39" s="32" t="n"/>
+      <c r="I39" s="30" t="n"/>
+      <c r="J39" s="30" t="n"/>
+      <c r="K39" s="32" t="n"/>
+      <c r="L39" s="30" t="n"/>
+      <c r="M39" s="31" t="n"/>
+      <c r="N39" s="31" t="n"/>
+      <c r="O39" s="31" t="n"/>
+      <c r="P39" s="31" t="n"/>
+      <c r="Q39" s="32" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="n"/>
-      <c r="B40" s="24" t="n"/>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="26" t="n"/>
-      <c r="E40" s="26" t="n"/>
-      <c r="F40" s="25" t="n"/>
-      <c r="G40" s="25" t="n"/>
-      <c r="H40" s="27" t="n"/>
-      <c r="I40" s="25" t="n"/>
-      <c r="J40" s="25" t="n"/>
-      <c r="K40" s="27" t="n"/>
-      <c r="L40" s="25" t="n"/>
-      <c r="M40" s="26" t="n"/>
-      <c r="N40" s="26" t="n"/>
-      <c r="O40" s="26" t="n"/>
-      <c r="P40" s="26" t="n"/>
-      <c r="Q40" s="27" t="n"/>
+      <c r="A40" s="25" t="n"/>
+      <c r="B40" s="25" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="27" t="n"/>
+      <c r="E40" s="27" t="n"/>
+      <c r="F40" s="26" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="28" t="n"/>
+      <c r="I40" s="26" t="n"/>
+      <c r="J40" s="26" t="n"/>
+      <c r="K40" s="28" t="n"/>
+      <c r="L40" s="26" t="n"/>
+      <c r="M40" s="27" t="n"/>
+      <c r="N40" s="27" t="n"/>
+      <c r="O40" s="27" t="n"/>
+      <c r="P40" s="27" t="n"/>
+      <c r="Q40" s="28" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="28" t="n"/>
-      <c r="B41" s="28" t="n"/>
-      <c r="C41" s="29" t="n"/>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="30" t="n"/>
-      <c r="F41" s="29" t="n"/>
-      <c r="G41" s="29" t="n"/>
-      <c r="H41" s="31" t="n"/>
-      <c r="I41" s="29" t="n"/>
-      <c r="J41" s="29" t="n"/>
-      <c r="K41" s="31" t="n"/>
-      <c r="L41" s="29" t="n"/>
-      <c r="M41" s="30" t="n"/>
-      <c r="N41" s="30" t="n"/>
-      <c r="O41" s="30" t="n"/>
-      <c r="P41" s="30" t="n"/>
-      <c r="Q41" s="31" t="n"/>
+      <c r="A41" s="29" t="n"/>
+      <c r="B41" s="29" t="n"/>
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="31" t="n"/>
+      <c r="E41" s="31" t="n"/>
+      <c r="F41" s="30" t="n"/>
+      <c r="G41" s="30" t="n"/>
+      <c r="H41" s="32" t="n"/>
+      <c r="I41" s="30" t="n"/>
+      <c r="J41" s="30" t="n"/>
+      <c r="K41" s="32" t="n"/>
+      <c r="L41" s="30" t="n"/>
+      <c r="M41" s="31" t="n"/>
+      <c r="N41" s="31" t="n"/>
+      <c r="O41" s="31" t="n"/>
+      <c r="P41" s="31" t="n"/>
+      <c r="Q41" s="32" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="24" t="n"/>
-      <c r="B42" s="24" t="n"/>
-      <c r="C42" s="25" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="25" t="n"/>
-      <c r="G42" s="25" t="n"/>
-      <c r="H42" s="27" t="n"/>
-      <c r="I42" s="25" t="n"/>
-      <c r="J42" s="25" t="n"/>
-      <c r="K42" s="27" t="n"/>
-      <c r="L42" s="25" t="n"/>
-      <c r="M42" s="26" t="n"/>
-      <c r="N42" s="26" t="n"/>
-      <c r="O42" s="26" t="n"/>
-      <c r="P42" s="26" t="n"/>
-      <c r="Q42" s="27" t="n"/>
+      <c r="A42" s="25" t="n"/>
+      <c r="B42" s="25" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="27" t="n"/>
+      <c r="E42" s="27" t="n"/>
+      <c r="F42" s="26" t="n"/>
+      <c r="G42" s="26" t="n"/>
+      <c r="H42" s="28" t="n"/>
+      <c r="I42" s="26" t="n"/>
+      <c r="J42" s="26" t="n"/>
+      <c r="K42" s="28" t="n"/>
+      <c r="L42" s="26" t="n"/>
+      <c r="M42" s="27" t="n"/>
+      <c r="N42" s="27" t="n"/>
+      <c r="O42" s="27" t="n"/>
+      <c r="P42" s="27" t="n"/>
+      <c r="Q42" s="28" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="28" t="n"/>
-      <c r="B43" s="28" t="n"/>
-      <c r="C43" s="29" t="n"/>
-      <c r="D43" s="30" t="n"/>
-      <c r="E43" s="30" t="n"/>
-      <c r="F43" s="29" t="n"/>
-      <c r="G43" s="29" t="n"/>
-      <c r="H43" s="31" t="n"/>
-      <c r="I43" s="29" t="n"/>
-      <c r="J43" s="29" t="n"/>
-      <c r="K43" s="31" t="n"/>
-      <c r="L43" s="29" t="n"/>
-      <c r="M43" s="30" t="n"/>
-      <c r="N43" s="30" t="n"/>
-      <c r="O43" s="30" t="n"/>
-      <c r="P43" s="30" t="n"/>
-      <c r="Q43" s="31" t="n"/>
+      <c r="A43" s="29" t="n"/>
+      <c r="B43" s="29" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="31" t="n"/>
+      <c r="F43" s="30" t="n"/>
+      <c r="G43" s="30" t="n"/>
+      <c r="H43" s="32" t="n"/>
+      <c r="I43" s="30" t="n"/>
+      <c r="J43" s="30" t="n"/>
+      <c r="K43" s="32" t="n"/>
+      <c r="L43" s="30" t="n"/>
+      <c r="M43" s="31" t="n"/>
+      <c r="N43" s="31" t="n"/>
+      <c r="O43" s="31" t="n"/>
+      <c r="P43" s="31" t="n"/>
+      <c r="Q43" s="32" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:Q43"/>
@@ -94159,7 +94188,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>LIEUX &amp; EXPOSITIONS</t>
         </is>
@@ -94172,408 +94201,408 @@
       <c r="G1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Lieux fréquentés par le cas et populations exposées.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Lieu</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Population exposée</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Nombre estimé</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Risque</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>Latitude</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>Longitude</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="n"/>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="26" t="n"/>
-      <c r="E4" s="27" t="n"/>
-      <c r="F4" s="26" t="n"/>
-      <c r="G4" s="26" t="n"/>
+      <c r="A4" s="26" t="n"/>
+      <c r="B4" s="28" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="27" t="n"/>
+      <c r="E4" s="28" t="n"/>
+      <c r="F4" s="27" t="n"/>
+      <c r="G4" s="27" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="n"/>
-      <c r="B5" s="31" t="n"/>
-      <c r="C5" s="29" t="n"/>
-      <c r="D5" s="30" t="n"/>
-      <c r="E5" s="31" t="n"/>
-      <c r="F5" s="30" t="n"/>
-      <c r="G5" s="30" t="n"/>
+      <c r="A5" s="30" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="31" t="n"/>
+      <c r="E5" s="32" t="n"/>
+      <c r="F5" s="31" t="n"/>
+      <c r="G5" s="31" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="25" t="n"/>
-      <c r="D6" s="26" t="n"/>
-      <c r="E6" s="27" t="n"/>
-      <c r="F6" s="26" t="n"/>
-      <c r="G6" s="26" t="n"/>
+      <c r="A6" s="26" t="n"/>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="27" t="n"/>
+      <c r="E6" s="28" t="n"/>
+      <c r="F6" s="27" t="n"/>
+      <c r="G6" s="27" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n"/>
-      <c r="B7" s="31" t="n"/>
-      <c r="C7" s="29" t="n"/>
-      <c r="D7" s="30" t="n"/>
-      <c r="E7" s="31" t="n"/>
-      <c r="F7" s="30" t="n"/>
-      <c r="G7" s="30" t="n"/>
+      <c r="A7" s="30" t="n"/>
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="30" t="n"/>
+      <c r="D7" s="31" t="n"/>
+      <c r="E7" s="32" t="n"/>
+      <c r="F7" s="31" t="n"/>
+      <c r="G7" s="31" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n"/>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="25" t="n"/>
-      <c r="D8" s="26" t="n"/>
-      <c r="E8" s="27" t="n"/>
-      <c r="F8" s="26" t="n"/>
-      <c r="G8" s="26" t="n"/>
+      <c r="A8" s="26" t="n"/>
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="27" t="n"/>
+      <c r="E8" s="28" t="n"/>
+      <c r="F8" s="27" t="n"/>
+      <c r="G8" s="27" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="31" t="n"/>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="30" t="n"/>
-      <c r="E9" s="31" t="n"/>
-      <c r="F9" s="30" t="n"/>
-      <c r="G9" s="30" t="n"/>
+      <c r="A9" s="30" t="n"/>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="30" t="n"/>
+      <c r="D9" s="31" t="n"/>
+      <c r="E9" s="32" t="n"/>
+      <c r="F9" s="31" t="n"/>
+      <c r="G9" s="31" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n"/>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="25" t="n"/>
-      <c r="D10" s="26" t="n"/>
-      <c r="E10" s="27" t="n"/>
-      <c r="F10" s="26" t="n"/>
-      <c r="G10" s="26" t="n"/>
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="27" t="n"/>
+      <c r="E10" s="28" t="n"/>
+      <c r="F10" s="27" t="n"/>
+      <c r="G10" s="27" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n"/>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="29" t="n"/>
-      <c r="D11" s="30" t="n"/>
-      <c r="E11" s="31" t="n"/>
-      <c r="F11" s="30" t="n"/>
-      <c r="G11" s="30" t="n"/>
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="31" t="n"/>
+      <c r="E11" s="32" t="n"/>
+      <c r="F11" s="31" t="n"/>
+      <c r="G11" s="31" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="26" t="n"/>
-      <c r="E12" s="27" t="n"/>
-      <c r="F12" s="26" t="n"/>
-      <c r="G12" s="26" t="n"/>
+      <c r="A12" s="26" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="27" t="n"/>
+      <c r="E12" s="28" t="n"/>
+      <c r="F12" s="27" t="n"/>
+      <c r="G12" s="27" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n"/>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="29" t="n"/>
-      <c r="D13" s="30" t="n"/>
-      <c r="E13" s="31" t="n"/>
-      <c r="F13" s="30" t="n"/>
-      <c r="G13" s="30" t="n"/>
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="31" t="n"/>
+      <c r="E13" s="32" t="n"/>
+      <c r="F13" s="31" t="n"/>
+      <c r="G13" s="31" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="n"/>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="26" t="n"/>
-      <c r="E14" s="27" t="n"/>
-      <c r="F14" s="26" t="n"/>
-      <c r="G14" s="26" t="n"/>
+      <c r="A14" s="26" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="27" t="n"/>
+      <c r="G14" s="27" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="n"/>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="30" t="n"/>
-      <c r="E15" s="31" t="n"/>
-      <c r="F15" s="30" t="n"/>
-      <c r="G15" s="30" t="n"/>
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="32" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="31" t="n"/>
+      <c r="E15" s="32" t="n"/>
+      <c r="F15" s="31" t="n"/>
+      <c r="G15" s="31" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="26" t="n"/>
-      <c r="E16" s="27" t="n"/>
-      <c r="F16" s="26" t="n"/>
-      <c r="G16" s="26" t="n"/>
+      <c r="A16" s="26" t="n"/>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="28" t="n"/>
+      <c r="F16" s="27" t="n"/>
+      <c r="G16" s="27" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n"/>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="30" t="n"/>
-      <c r="E17" s="31" t="n"/>
-      <c r="F17" s="30" t="n"/>
-      <c r="G17" s="30" t="n"/>
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="31" t="n"/>
+      <c r="E17" s="32" t="n"/>
+      <c r="F17" s="31" t="n"/>
+      <c r="G17" s="31" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="26" t="n"/>
-      <c r="E18" s="27" t="n"/>
-      <c r="F18" s="26" t="n"/>
-      <c r="G18" s="26" t="n"/>
+      <c r="A18" s="26" t="n"/>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="27" t="n"/>
+      <c r="E18" s="28" t="n"/>
+      <c r="F18" s="27" t="n"/>
+      <c r="G18" s="27" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="31" t="n"/>
-      <c r="C19" s="29" t="n"/>
-      <c r="D19" s="30" t="n"/>
-      <c r="E19" s="31" t="n"/>
-      <c r="F19" s="30" t="n"/>
-      <c r="G19" s="30" t="n"/>
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="31" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="31" t="n"/>
+      <c r="G19" s="31" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="26" t="n"/>
-      <c r="E20" s="27" t="n"/>
-      <c r="F20" s="26" t="n"/>
-      <c r="G20" s="26" t="n"/>
+      <c r="A20" s="26" t="n"/>
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="27" t="n"/>
+      <c r="E20" s="28" t="n"/>
+      <c r="F20" s="27" t="n"/>
+      <c r="G20" s="27" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="31" t="n"/>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="30" t="n"/>
-      <c r="E21" s="31" t="n"/>
-      <c r="F21" s="30" t="n"/>
-      <c r="G21" s="30" t="n"/>
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="30" t="n"/>
+      <c r="D21" s="31" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="31" t="n"/>
+      <c r="G21" s="31" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="n"/>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="26" t="n"/>
-      <c r="E22" s="27" t="n"/>
-      <c r="F22" s="26" t="n"/>
-      <c r="G22" s="26" t="n"/>
+      <c r="A22" s="26" t="n"/>
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="27" t="n"/>
+      <c r="E22" s="28" t="n"/>
+      <c r="F22" s="27" t="n"/>
+      <c r="G22" s="27" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="31" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="30" t="n"/>
-      <c r="E23" s="31" t="n"/>
-      <c r="F23" s="30" t="n"/>
-      <c r="G23" s="30" t="n"/>
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="31" t="n"/>
+      <c r="E23" s="32" t="n"/>
+      <c r="F23" s="31" t="n"/>
+      <c r="G23" s="31" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="n"/>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="26" t="n"/>
-      <c r="E24" s="27" t="n"/>
-      <c r="F24" s="26" t="n"/>
-      <c r="G24" s="26" t="n"/>
+      <c r="A24" s="26" t="n"/>
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="28" t="n"/>
+      <c r="F24" s="27" t="n"/>
+      <c r="G24" s="27" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="31" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="30" t="n"/>
-      <c r="E25" s="31" t="n"/>
-      <c r="F25" s="30" t="n"/>
-      <c r="G25" s="30" t="n"/>
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="31" t="n"/>
+      <c r="E25" s="32" t="n"/>
+      <c r="F25" s="31" t="n"/>
+      <c r="G25" s="31" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="n"/>
-      <c r="B26" s="27" t="n"/>
-      <c r="C26" s="25" t="n"/>
-      <c r="D26" s="26" t="n"/>
-      <c r="E26" s="27" t="n"/>
-      <c r="F26" s="26" t="n"/>
-      <c r="G26" s="26" t="n"/>
+      <c r="A26" s="26" t="n"/>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="27" t="n"/>
+      <c r="E26" s="28" t="n"/>
+      <c r="F26" s="27" t="n"/>
+      <c r="G26" s="27" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="30" t="n"/>
-      <c r="E27" s="31" t="n"/>
-      <c r="F27" s="30" t="n"/>
-      <c r="G27" s="30" t="n"/>
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="31" t="n"/>
+      <c r="E27" s="32" t="n"/>
+      <c r="F27" s="31" t="n"/>
+      <c r="G27" s="31" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="n"/>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="26" t="n"/>
-      <c r="E28" s="27" t="n"/>
-      <c r="F28" s="26" t="n"/>
-      <c r="G28" s="26" t="n"/>
+      <c r="A28" s="26" t="n"/>
+      <c r="B28" s="28" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="28" t="n"/>
+      <c r="F28" s="27" t="n"/>
+      <c r="G28" s="27" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="n"/>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="29" t="n"/>
-      <c r="D29" s="30" t="n"/>
-      <c r="E29" s="31" t="n"/>
-      <c r="F29" s="30" t="n"/>
-      <c r="G29" s="30" t="n"/>
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="32" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="31" t="n"/>
+      <c r="E29" s="32" t="n"/>
+      <c r="F29" s="31" t="n"/>
+      <c r="G29" s="31" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="n"/>
-      <c r="B30" s="27" t="n"/>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="26" t="n"/>
-      <c r="E30" s="27" t="n"/>
-      <c r="F30" s="26" t="n"/>
-      <c r="G30" s="26" t="n"/>
+      <c r="A30" s="26" t="n"/>
+      <c r="B30" s="28" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="27" t="n"/>
+      <c r="E30" s="28" t="n"/>
+      <c r="F30" s="27" t="n"/>
+      <c r="G30" s="27" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="31" t="n"/>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="30" t="n"/>
-      <c r="E31" s="31" t="n"/>
-      <c r="F31" s="30" t="n"/>
-      <c r="G31" s="30" t="n"/>
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="32" t="n"/>
+      <c r="C31" s="30" t="n"/>
+      <c r="D31" s="31" t="n"/>
+      <c r="E31" s="32" t="n"/>
+      <c r="F31" s="31" t="n"/>
+      <c r="G31" s="31" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="25" t="n"/>
-      <c r="D32" s="26" t="n"/>
-      <c r="E32" s="27" t="n"/>
-      <c r="F32" s="26" t="n"/>
-      <c r="G32" s="26" t="n"/>
+      <c r="A32" s="26" t="n"/>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="27" t="n"/>
+      <c r="E32" s="28" t="n"/>
+      <c r="F32" s="27" t="n"/>
+      <c r="G32" s="27" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="n"/>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="30" t="n"/>
-      <c r="E33" s="31" t="n"/>
-      <c r="F33" s="30" t="n"/>
-      <c r="G33" s="30" t="n"/>
+      <c r="A33" s="30" t="n"/>
+      <c r="B33" s="32" t="n"/>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="31" t="n"/>
+      <c r="E33" s="32" t="n"/>
+      <c r="F33" s="31" t="n"/>
+      <c r="G33" s="31" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="25" t="n"/>
-      <c r="D34" s="26" t="n"/>
-      <c r="E34" s="27" t="n"/>
-      <c r="F34" s="26" t="n"/>
-      <c r="G34" s="26" t="n"/>
+      <c r="A34" s="26" t="n"/>
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="27" t="n"/>
+      <c r="E34" s="28" t="n"/>
+      <c r="F34" s="27" t="n"/>
+      <c r="G34" s="27" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="n"/>
-      <c r="B35" s="31" t="n"/>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="30" t="n"/>
-      <c r="E35" s="31" t="n"/>
-      <c r="F35" s="30" t="n"/>
-      <c r="G35" s="30" t="n"/>
+      <c r="A35" s="30" t="n"/>
+      <c r="B35" s="32" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="31" t="n"/>
+      <c r="E35" s="32" t="n"/>
+      <c r="F35" s="31" t="n"/>
+      <c r="G35" s="31" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="n"/>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="25" t="n"/>
-      <c r="D36" s="26" t="n"/>
-      <c r="E36" s="27" t="n"/>
-      <c r="F36" s="26" t="n"/>
-      <c r="G36" s="26" t="n"/>
+      <c r="A36" s="26" t="n"/>
+      <c r="B36" s="28" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="27" t="n"/>
+      <c r="E36" s="28" t="n"/>
+      <c r="F36" s="27" t="n"/>
+      <c r="G36" s="27" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="n"/>
-      <c r="B37" s="31" t="n"/>
-      <c r="C37" s="29" t="n"/>
-      <c r="D37" s="30" t="n"/>
-      <c r="E37" s="31" t="n"/>
-      <c r="F37" s="30" t="n"/>
-      <c r="G37" s="30" t="n"/>
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="32" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="31" t="n"/>
+      <c r="E37" s="32" t="n"/>
+      <c r="F37" s="31" t="n"/>
+      <c r="G37" s="31" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="25" t="n"/>
-      <c r="B38" s="27" t="n"/>
-      <c r="C38" s="25" t="n"/>
-      <c r="D38" s="26" t="n"/>
-      <c r="E38" s="27" t="n"/>
-      <c r="F38" s="26" t="n"/>
-      <c r="G38" s="26" t="n"/>
+      <c r="A38" s="26" t="n"/>
+      <c r="B38" s="28" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="27" t="n"/>
+      <c r="E38" s="28" t="n"/>
+      <c r="F38" s="27" t="n"/>
+      <c r="G38" s="27" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="n"/>
-      <c r="B39" s="31" t="n"/>
-      <c r="C39" s="29" t="n"/>
-      <c r="D39" s="30" t="n"/>
-      <c r="E39" s="31" t="n"/>
-      <c r="F39" s="30" t="n"/>
-      <c r="G39" s="30" t="n"/>
+      <c r="A39" s="30" t="n"/>
+      <c r="B39" s="32" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="31" t="n"/>
+      <c r="E39" s="32" t="n"/>
+      <c r="F39" s="31" t="n"/>
+      <c r="G39" s="31" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="26" t="n"/>
-      <c r="E40" s="27" t="n"/>
-      <c r="F40" s="26" t="n"/>
-      <c r="G40" s="26" t="n"/>
+      <c r="A40" s="26" t="n"/>
+      <c r="B40" s="28" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="27" t="n"/>
+      <c r="E40" s="28" t="n"/>
+      <c r="F40" s="27" t="n"/>
+      <c r="G40" s="27" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="n"/>
-      <c r="B41" s="31" t="n"/>
-      <c r="C41" s="29" t="n"/>
-      <c r="D41" s="30" t="n"/>
-      <c r="E41" s="31" t="n"/>
-      <c r="F41" s="30" t="n"/>
-      <c r="G41" s="30" t="n"/>
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="32" t="n"/>
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="31" t="n"/>
+      <c r="E41" s="32" t="n"/>
+      <c r="F41" s="31" t="n"/>
+      <c r="G41" s="31" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="n"/>
-      <c r="B42" s="27" t="n"/>
-      <c r="C42" s="25" t="n"/>
-      <c r="D42" s="26" t="n"/>
-      <c r="E42" s="27" t="n"/>
-      <c r="F42" s="26" t="n"/>
-      <c r="G42" s="26" t="n"/>
+      <c r="A42" s="26" t="n"/>
+      <c r="B42" s="28" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="27" t="n"/>
+      <c r="E42" s="28" t="n"/>
+      <c r="F42" s="27" t="n"/>
+      <c r="G42" s="27" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="n"/>
-      <c r="B43" s="31" t="n"/>
-      <c r="C43" s="29" t="n"/>
-      <c r="D43" s="30" t="n"/>
-      <c r="E43" s="31" t="n"/>
-      <c r="F43" s="30" t="n"/>
-      <c r="G43" s="30" t="n"/>
+      <c r="A43" s="30" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="31" t="n"/>
+      <c r="E43" s="32" t="n"/>
+      <c r="F43" s="31" t="n"/>
+      <c r="G43" s="31" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G43"/>
@@ -94668,7 +94697,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>CONTACTS À IDENTIFIER / SUIVRE</t>
         </is>
@@ -94682,453 +94711,453 @@
       <c r="H1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>« ? » = nombre inconnu (jamais 0 par défaut). Le « Minimum documenté » est calculé par l'outil.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Catégorie</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Lien avec le cas</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Nombre (? si inconnu)</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Libellé</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Suivis</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>Risque</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>Lieu de contact</t>
         </is>
       </c>
-      <c r="H3" s="23" t="inlineStr">
+      <c r="H3" s="24" t="inlineStr">
         <is>
           <t>Dernier contact</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="26" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="26" t="n"/>
-      <c r="F4" s="27" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="24" t="n"/>
+      <c r="A4" s="26" t="n"/>
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="27" t="n"/>
+      <c r="F4" s="28" t="n"/>
+      <c r="G4" s="26" t="n"/>
+      <c r="H4" s="25" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="n"/>
-      <c r="B5" s="29" t="n"/>
-      <c r="C5" s="30" t="n"/>
-      <c r="D5" s="29" t="n"/>
-      <c r="E5" s="30" t="n"/>
-      <c r="F5" s="31" t="n"/>
-      <c r="G5" s="29" t="n"/>
-      <c r="H5" s="28" t="n"/>
+      <c r="A5" s="30" t="n"/>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="31" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="31" t="n"/>
+      <c r="F5" s="32" t="n"/>
+      <c r="G5" s="30" t="n"/>
+      <c r="H5" s="29" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="25" t="n"/>
-      <c r="C6" s="26" t="n"/>
-      <c r="D6" s="25" t="n"/>
-      <c r="E6" s="26" t="n"/>
-      <c r="F6" s="27" t="n"/>
-      <c r="G6" s="25" t="n"/>
-      <c r="H6" s="24" t="n"/>
+      <c r="A6" s="26" t="n"/>
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="27" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="27" t="n"/>
+      <c r="F6" s="28" t="n"/>
+      <c r="G6" s="26" t="n"/>
+      <c r="H6" s="25" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n"/>
-      <c r="B7" s="29" t="n"/>
-      <c r="C7" s="30" t="n"/>
-      <c r="D7" s="29" t="n"/>
-      <c r="E7" s="30" t="n"/>
-      <c r="F7" s="31" t="n"/>
-      <c r="G7" s="29" t="n"/>
-      <c r="H7" s="28" t="n"/>
+      <c r="A7" s="30" t="n"/>
+      <c r="B7" s="30" t="n"/>
+      <c r="C7" s="31" t="n"/>
+      <c r="D7" s="30" t="n"/>
+      <c r="E7" s="31" t="n"/>
+      <c r="F7" s="32" t="n"/>
+      <c r="G7" s="30" t="n"/>
+      <c r="H7" s="29" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n"/>
-      <c r="B8" s="25" t="n"/>
-      <c r="C8" s="26" t="n"/>
-      <c r="D8" s="25" t="n"/>
-      <c r="E8" s="26" t="n"/>
-      <c r="F8" s="27" t="n"/>
-      <c r="G8" s="25" t="n"/>
-      <c r="H8" s="24" t="n"/>
+      <c r="A8" s="26" t="n"/>
+      <c r="B8" s="26" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="27" t="n"/>
+      <c r="F8" s="28" t="n"/>
+      <c r="G8" s="26" t="n"/>
+      <c r="H8" s="25" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="29" t="n"/>
-      <c r="C9" s="30" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="30" t="n"/>
-      <c r="F9" s="31" t="n"/>
-      <c r="G9" s="29" t="n"/>
-      <c r="H9" s="28" t="n"/>
+      <c r="A9" s="30" t="n"/>
+      <c r="B9" s="30" t="n"/>
+      <c r="C9" s="31" t="n"/>
+      <c r="D9" s="30" t="n"/>
+      <c r="E9" s="31" t="n"/>
+      <c r="F9" s="32" t="n"/>
+      <c r="G9" s="30" t="n"/>
+      <c r="H9" s="29" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n"/>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="26" t="n"/>
-      <c r="D10" s="25" t="n"/>
-      <c r="E10" s="26" t="n"/>
-      <c r="F10" s="27" t="n"/>
-      <c r="G10" s="25" t="n"/>
-      <c r="H10" s="24" t="n"/>
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="27" t="n"/>
+      <c r="F10" s="28" t="n"/>
+      <c r="G10" s="26" t="n"/>
+      <c r="H10" s="25" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n"/>
-      <c r="B11" s="29" t="n"/>
-      <c r="C11" s="30" t="n"/>
-      <c r="D11" s="29" t="n"/>
-      <c r="E11" s="30" t="n"/>
-      <c r="F11" s="31" t="n"/>
-      <c r="G11" s="29" t="n"/>
-      <c r="H11" s="28" t="n"/>
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="31" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="31" t="n"/>
+      <c r="F11" s="32" t="n"/>
+      <c r="G11" s="30" t="n"/>
+      <c r="H11" s="29" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="26" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="26" t="n"/>
-      <c r="F12" s="27" t="n"/>
-      <c r="G12" s="25" t="n"/>
-      <c r="H12" s="24" t="n"/>
+      <c r="A12" s="26" t="n"/>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="27" t="n"/>
+      <c r="F12" s="28" t="n"/>
+      <c r="G12" s="26" t="n"/>
+      <c r="H12" s="25" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n"/>
-      <c r="B13" s="29" t="n"/>
-      <c r="C13" s="30" t="n"/>
-      <c r="D13" s="29" t="n"/>
-      <c r="E13" s="30" t="n"/>
-      <c r="F13" s="31" t="n"/>
-      <c r="G13" s="29" t="n"/>
-      <c r="H13" s="28" t="n"/>
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="31" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="31" t="n"/>
+      <c r="F13" s="32" t="n"/>
+      <c r="G13" s="30" t="n"/>
+      <c r="H13" s="29" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="n"/>
-      <c r="B14" s="25" t="n"/>
-      <c r="C14" s="26" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="26" t="n"/>
-      <c r="F14" s="27" t="n"/>
-      <c r="G14" s="25" t="n"/>
-      <c r="H14" s="24" t="n"/>
+      <c r="A14" s="26" t="n"/>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="26" t="n"/>
+      <c r="H14" s="25" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="n"/>
-      <c r="B15" s="29" t="n"/>
-      <c r="C15" s="30" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="30" t="n"/>
-      <c r="F15" s="31" t="n"/>
-      <c r="G15" s="29" t="n"/>
-      <c r="H15" s="28" t="n"/>
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="31" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="31" t="n"/>
+      <c r="F15" s="32" t="n"/>
+      <c r="G15" s="30" t="n"/>
+      <c r="H15" s="29" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="26" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="26" t="n"/>
-      <c r="F16" s="27" t="n"/>
-      <c r="G16" s="25" t="n"/>
-      <c r="H16" s="24" t="n"/>
+      <c r="A16" s="26" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="28" t="n"/>
+      <c r="G16" s="26" t="n"/>
+      <c r="H16" s="25" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n"/>
-      <c r="B17" s="29" t="n"/>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="30" t="n"/>
-      <c r="F17" s="31" t="n"/>
-      <c r="G17" s="29" t="n"/>
-      <c r="H17" s="28" t="n"/>
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="31" t="n"/>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="31" t="n"/>
+      <c r="F17" s="32" t="n"/>
+      <c r="G17" s="30" t="n"/>
+      <c r="H17" s="29" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="26" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="26" t="n"/>
-      <c r="F18" s="27" t="n"/>
-      <c r="G18" s="25" t="n"/>
-      <c r="H18" s="24" t="n"/>
+      <c r="A18" s="26" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="27" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="27" t="n"/>
+      <c r="F18" s="28" t="n"/>
+      <c r="G18" s="26" t="n"/>
+      <c r="H18" s="25" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="29" t="n"/>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="29" t="n"/>
-      <c r="E19" s="30" t="n"/>
-      <c r="F19" s="31" t="n"/>
-      <c r="G19" s="29" t="n"/>
-      <c r="H19" s="28" t="n"/>
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="31" t="n"/>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="31" t="n"/>
+      <c r="F19" s="32" t="n"/>
+      <c r="G19" s="30" t="n"/>
+      <c r="H19" s="29" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="26" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="26" t="n"/>
-      <c r="F20" s="27" t="n"/>
-      <c r="G20" s="25" t="n"/>
-      <c r="H20" s="24" t="n"/>
+      <c r="A20" s="26" t="n"/>
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="28" t="n"/>
+      <c r="G20" s="26" t="n"/>
+      <c r="H20" s="25" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="29" t="n"/>
-      <c r="E21" s="30" t="n"/>
-      <c r="F21" s="31" t="n"/>
-      <c r="G21" s="29" t="n"/>
-      <c r="H21" s="28" t="n"/>
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="30" t="n"/>
+      <c r="C21" s="31" t="n"/>
+      <c r="D21" s="30" t="n"/>
+      <c r="E21" s="31" t="n"/>
+      <c r="F21" s="32" t="n"/>
+      <c r="G21" s="30" t="n"/>
+      <c r="H21" s="29" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="n"/>
-      <c r="B22" s="25" t="n"/>
-      <c r="C22" s="26" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="26" t="n"/>
-      <c r="F22" s="27" t="n"/>
-      <c r="G22" s="25" t="n"/>
-      <c r="H22" s="24" t="n"/>
+      <c r="A22" s="26" t="n"/>
+      <c r="B22" s="26" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="28" t="n"/>
+      <c r="G22" s="26" t="n"/>
+      <c r="H22" s="25" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="30" t="n"/>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="30" t="n"/>
-      <c r="F23" s="31" t="n"/>
-      <c r="G23" s="29" t="n"/>
-      <c r="H23" s="28" t="n"/>
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="31" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="31" t="n"/>
+      <c r="F23" s="32" t="n"/>
+      <c r="G23" s="30" t="n"/>
+      <c r="H23" s="29" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="n"/>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="26" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="26" t="n"/>
-      <c r="F24" s="27" t="n"/>
-      <c r="G24" s="25" t="n"/>
-      <c r="H24" s="24" t="n"/>
+      <c r="A24" s="26" t="n"/>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="28" t="n"/>
+      <c r="G24" s="26" t="n"/>
+      <c r="H24" s="25" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="30" t="n"/>
-      <c r="D25" s="29" t="n"/>
-      <c r="E25" s="30" t="n"/>
-      <c r="F25" s="31" t="n"/>
-      <c r="G25" s="29" t="n"/>
-      <c r="H25" s="28" t="n"/>
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="30" t="n"/>
+      <c r="C25" s="31" t="n"/>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="31" t="n"/>
+      <c r="F25" s="32" t="n"/>
+      <c r="G25" s="30" t="n"/>
+      <c r="H25" s="29" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="n"/>
-      <c r="B26" s="25" t="n"/>
-      <c r="C26" s="26" t="n"/>
-      <c r="D26" s="25" t="n"/>
-      <c r="E26" s="26" t="n"/>
-      <c r="F26" s="27" t="n"/>
-      <c r="G26" s="25" t="n"/>
-      <c r="H26" s="24" t="n"/>
+      <c r="A26" s="26" t="n"/>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="27" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="27" t="n"/>
+      <c r="F26" s="28" t="n"/>
+      <c r="G26" s="26" t="n"/>
+      <c r="H26" s="25" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="30" t="n"/>
-      <c r="D27" s="29" t="n"/>
-      <c r="E27" s="30" t="n"/>
-      <c r="F27" s="31" t="n"/>
-      <c r="G27" s="29" t="n"/>
-      <c r="H27" s="28" t="n"/>
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="31" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="31" t="n"/>
+      <c r="F27" s="32" t="n"/>
+      <c r="G27" s="30" t="n"/>
+      <c r="H27" s="29" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="n"/>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="26" t="n"/>
-      <c r="D28" s="25" t="n"/>
-      <c r="E28" s="26" t="n"/>
-      <c r="F28" s="27" t="n"/>
-      <c r="G28" s="25" t="n"/>
-      <c r="H28" s="24" t="n"/>
+      <c r="A28" s="26" t="n"/>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="26" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="28" t="n"/>
+      <c r="G28" s="26" t="n"/>
+      <c r="H28" s="25" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="n"/>
-      <c r="B29" s="29" t="n"/>
-      <c r="C29" s="30" t="n"/>
-      <c r="D29" s="29" t="n"/>
-      <c r="E29" s="30" t="n"/>
-      <c r="F29" s="31" t="n"/>
-      <c r="G29" s="29" t="n"/>
-      <c r="H29" s="28" t="n"/>
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="30" t="n"/>
+      <c r="C29" s="31" t="n"/>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="31" t="n"/>
+      <c r="F29" s="32" t="n"/>
+      <c r="G29" s="30" t="n"/>
+      <c r="H29" s="29" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="n"/>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="26" t="n"/>
-      <c r="D30" s="25" t="n"/>
-      <c r="E30" s="26" t="n"/>
-      <c r="F30" s="27" t="n"/>
-      <c r="G30" s="25" t="n"/>
-      <c r="H30" s="24" t="n"/>
+      <c r="A30" s="26" t="n"/>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="27" t="n"/>
+      <c r="F30" s="28" t="n"/>
+      <c r="G30" s="26" t="n"/>
+      <c r="H30" s="25" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="29" t="n"/>
-      <c r="C31" s="30" t="n"/>
-      <c r="D31" s="29" t="n"/>
-      <c r="E31" s="30" t="n"/>
-      <c r="F31" s="31" t="n"/>
-      <c r="G31" s="29" t="n"/>
-      <c r="H31" s="28" t="n"/>
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="30" t="n"/>
+      <c r="C31" s="31" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="31" t="n"/>
+      <c r="F31" s="32" t="n"/>
+      <c r="G31" s="30" t="n"/>
+      <c r="H31" s="29" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="26" t="n"/>
-      <c r="D32" s="25" t="n"/>
-      <c r="E32" s="26" t="n"/>
-      <c r="F32" s="27" t="n"/>
-      <c r="G32" s="25" t="n"/>
-      <c r="H32" s="24" t="n"/>
+      <c r="A32" s="26" t="n"/>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="27" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="27" t="n"/>
+      <c r="F32" s="28" t="n"/>
+      <c r="G32" s="26" t="n"/>
+      <c r="H32" s="25" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="n"/>
-      <c r="B33" s="29" t="n"/>
-      <c r="C33" s="30" t="n"/>
-      <c r="D33" s="29" t="n"/>
-      <c r="E33" s="30" t="n"/>
-      <c r="F33" s="31" t="n"/>
-      <c r="G33" s="29" t="n"/>
-      <c r="H33" s="28" t="n"/>
+      <c r="A33" s="30" t="n"/>
+      <c r="B33" s="30" t="n"/>
+      <c r="C33" s="31" t="n"/>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="31" t="n"/>
+      <c r="F33" s="32" t="n"/>
+      <c r="G33" s="30" t="n"/>
+      <c r="H33" s="29" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="26" t="n"/>
-      <c r="D34" s="25" t="n"/>
-      <c r="E34" s="26" t="n"/>
-      <c r="F34" s="27" t="n"/>
-      <c r="G34" s="25" t="n"/>
-      <c r="H34" s="24" t="n"/>
+      <c r="A34" s="26" t="n"/>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="27" t="n"/>
+      <c r="D34" s="26" t="n"/>
+      <c r="E34" s="27" t="n"/>
+      <c r="F34" s="28" t="n"/>
+      <c r="G34" s="26" t="n"/>
+      <c r="H34" s="25" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="n"/>
-      <c r="B35" s="29" t="n"/>
-      <c r="C35" s="30" t="n"/>
-      <c r="D35" s="29" t="n"/>
-      <c r="E35" s="30" t="n"/>
-      <c r="F35" s="31" t="n"/>
-      <c r="G35" s="29" t="n"/>
-      <c r="H35" s="28" t="n"/>
+      <c r="A35" s="30" t="n"/>
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="31" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="31" t="n"/>
+      <c r="F35" s="32" t="n"/>
+      <c r="G35" s="30" t="n"/>
+      <c r="H35" s="29" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="n"/>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="26" t="n"/>
-      <c r="D36" s="25" t="n"/>
-      <c r="E36" s="26" t="n"/>
-      <c r="F36" s="27" t="n"/>
-      <c r="G36" s="25" t="n"/>
-      <c r="H36" s="24" t="n"/>
+      <c r="A36" s="26" t="n"/>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="27" t="n"/>
+      <c r="D36" s="26" t="n"/>
+      <c r="E36" s="27" t="n"/>
+      <c r="F36" s="28" t="n"/>
+      <c r="G36" s="26" t="n"/>
+      <c r="H36" s="25" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="n"/>
-      <c r="B37" s="29" t="n"/>
-      <c r="C37" s="30" t="n"/>
-      <c r="D37" s="29" t="n"/>
-      <c r="E37" s="30" t="n"/>
-      <c r="F37" s="31" t="n"/>
-      <c r="G37" s="29" t="n"/>
-      <c r="H37" s="28" t="n"/>
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="30" t="n"/>
+      <c r="C37" s="31" t="n"/>
+      <c r="D37" s="30" t="n"/>
+      <c r="E37" s="31" t="n"/>
+      <c r="F37" s="32" t="n"/>
+      <c r="G37" s="30" t="n"/>
+      <c r="H37" s="29" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="25" t="n"/>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="26" t="n"/>
-      <c r="D38" s="25" t="n"/>
-      <c r="E38" s="26" t="n"/>
-      <c r="F38" s="27" t="n"/>
-      <c r="G38" s="25" t="n"/>
-      <c r="H38" s="24" t="n"/>
+      <c r="A38" s="26" t="n"/>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="27" t="n"/>
+      <c r="D38" s="26" t="n"/>
+      <c r="E38" s="27" t="n"/>
+      <c r="F38" s="28" t="n"/>
+      <c r="G38" s="26" t="n"/>
+      <c r="H38" s="25" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="n"/>
-      <c r="B39" s="29" t="n"/>
-      <c r="C39" s="30" t="n"/>
-      <c r="D39" s="29" t="n"/>
-      <c r="E39" s="30" t="n"/>
-      <c r="F39" s="31" t="n"/>
-      <c r="G39" s="29" t="n"/>
-      <c r="H39" s="28" t="n"/>
+      <c r="A39" s="30" t="n"/>
+      <c r="B39" s="30" t="n"/>
+      <c r="C39" s="31" t="n"/>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="31" t="n"/>
+      <c r="F39" s="32" t="n"/>
+      <c r="G39" s="30" t="n"/>
+      <c r="H39" s="29" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="26" t="n"/>
-      <c r="D40" s="25" t="n"/>
-      <c r="E40" s="26" t="n"/>
-      <c r="F40" s="27" t="n"/>
-      <c r="G40" s="25" t="n"/>
-      <c r="H40" s="24" t="n"/>
+      <c r="A40" s="26" t="n"/>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="27" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="27" t="n"/>
+      <c r="F40" s="28" t="n"/>
+      <c r="G40" s="26" t="n"/>
+      <c r="H40" s="25" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="n"/>
-      <c r="B41" s="29" t="n"/>
-      <c r="C41" s="30" t="n"/>
-      <c r="D41" s="29" t="n"/>
-      <c r="E41" s="30" t="n"/>
-      <c r="F41" s="31" t="n"/>
-      <c r="G41" s="29" t="n"/>
-      <c r="H41" s="28" t="n"/>
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="30" t="n"/>
+      <c r="C41" s="31" t="n"/>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="31" t="n"/>
+      <c r="F41" s="32" t="n"/>
+      <c r="G41" s="30" t="n"/>
+      <c r="H41" s="29" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="n"/>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="26" t="n"/>
-      <c r="D42" s="25" t="n"/>
-      <c r="E42" s="26" t="n"/>
-      <c r="F42" s="27" t="n"/>
-      <c r="G42" s="25" t="n"/>
-      <c r="H42" s="24" t="n"/>
+      <c r="A42" s="26" t="n"/>
+      <c r="B42" s="26" t="n"/>
+      <c r="C42" s="27" t="n"/>
+      <c r="D42" s="26" t="n"/>
+      <c r="E42" s="27" t="n"/>
+      <c r="F42" s="28" t="n"/>
+      <c r="G42" s="26" t="n"/>
+      <c r="H42" s="25" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="n"/>
-      <c r="B43" s="29" t="n"/>
-      <c r="C43" s="30" t="n"/>
-      <c r="D43" s="29" t="n"/>
-      <c r="E43" s="30" t="n"/>
-      <c r="F43" s="31" t="n"/>
-      <c r="G43" s="29" t="n"/>
-      <c r="H43" s="28" t="n"/>
+      <c r="A43" s="30" t="n"/>
+      <c r="B43" s="30" t="n"/>
+      <c r="C43" s="31" t="n"/>
+      <c r="D43" s="30" t="n"/>
+      <c r="E43" s="31" t="n"/>
+      <c r="F43" s="32" t="n"/>
+      <c r="G43" s="30" t="n"/>
+      <c r="H43" s="29" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:H43"/>
@@ -95217,7 +95246,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>PCI / DÉCONTAMINATION</t>
         </is>
@@ -95228,318 +95257,318 @@
       <c r="E1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Documenter date, équipe et produit pour chaque site.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Site</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Date</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Équipe</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Produit</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="n"/>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="24" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
+      <c r="A4" s="26" t="n"/>
+      <c r="B4" s="28" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="26" t="n"/>
+      <c r="E4" s="26" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="n"/>
-      <c r="B5" s="31" t="n"/>
-      <c r="C5" s="28" t="n"/>
-      <c r="D5" s="29" t="n"/>
-      <c r="E5" s="29" t="n"/>
+      <c r="A5" s="30" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="29" t="n"/>
+      <c r="D5" s="30" t="n"/>
+      <c r="E5" s="30" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="24" t="n"/>
-      <c r="D6" s="25" t="n"/>
-      <c r="E6" s="25" t="n"/>
+      <c r="A6" s="26" t="n"/>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="25" t="n"/>
+      <c r="D6" s="26" t="n"/>
+      <c r="E6" s="26" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n"/>
-      <c r="B7" s="31" t="n"/>
-      <c r="C7" s="28" t="n"/>
-      <c r="D7" s="29" t="n"/>
-      <c r="E7" s="29" t="n"/>
+      <c r="A7" s="30" t="n"/>
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="29" t="n"/>
+      <c r="D7" s="30" t="n"/>
+      <c r="E7" s="30" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n"/>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="24" t="n"/>
-      <c r="D8" s="25" t="n"/>
-      <c r="E8" s="25" t="n"/>
+      <c r="A8" s="26" t="n"/>
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="26" t="n"/>
+      <c r="E8" s="26" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="31" t="n"/>
-      <c r="C9" s="28" t="n"/>
-      <c r="D9" s="29" t="n"/>
-      <c r="E9" s="29" t="n"/>
+      <c r="A9" s="30" t="n"/>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="29" t="n"/>
+      <c r="D9" s="30" t="n"/>
+      <c r="E9" s="30" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n"/>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="24" t="n"/>
-      <c r="D10" s="25" t="n"/>
-      <c r="E10" s="25" t="n"/>
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="25" t="n"/>
+      <c r="D10" s="26" t="n"/>
+      <c r="E10" s="26" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n"/>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="28" t="n"/>
-      <c r="D11" s="29" t="n"/>
-      <c r="E11" s="29" t="n"/>
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="29" t="n"/>
+      <c r="D11" s="30" t="n"/>
+      <c r="E11" s="30" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
+      <c r="A12" s="26" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="26" t="n"/>
+      <c r="E12" s="26" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n"/>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="28" t="n"/>
-      <c r="D13" s="29" t="n"/>
-      <c r="E13" s="29" t="n"/>
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="29" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="30" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="n"/>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
+      <c r="A14" s="26" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="25" t="n"/>
+      <c r="D14" s="26" t="n"/>
+      <c r="E14" s="26" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="n"/>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="28" t="n"/>
-      <c r="D15" s="29" t="n"/>
-      <c r="E15" s="29" t="n"/>
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="32" t="n"/>
+      <c r="C15" s="29" t="n"/>
+      <c r="D15" s="30" t="n"/>
+      <c r="E15" s="30" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="24" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
+      <c r="A16" s="26" t="n"/>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="26" t="n"/>
+      <c r="E16" s="26" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n"/>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="28" t="n"/>
-      <c r="D17" s="29" t="n"/>
-      <c r="E17" s="29" t="n"/>
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="29" t="n"/>
+      <c r="D17" s="30" t="n"/>
+      <c r="E17" s="30" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="24" t="n"/>
-      <c r="D18" s="25" t="n"/>
-      <c r="E18" s="25" t="n"/>
+      <c r="A18" s="26" t="n"/>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="26" t="n"/>
+      <c r="E18" s="26" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="31" t="n"/>
-      <c r="C19" s="28" t="n"/>
-      <c r="D19" s="29" t="n"/>
-      <c r="E19" s="29" t="n"/>
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="29" t="n"/>
+      <c r="D19" s="30" t="n"/>
+      <c r="E19" s="30" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="24" t="n"/>
-      <c r="D20" s="25" t="n"/>
-      <c r="E20" s="25" t="n"/>
+      <c r="A20" s="26" t="n"/>
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="26" t="n"/>
+      <c r="E20" s="26" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="31" t="n"/>
-      <c r="C21" s="28" t="n"/>
-      <c r="D21" s="29" t="n"/>
-      <c r="E21" s="29" t="n"/>
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="29" t="n"/>
+      <c r="D21" s="30" t="n"/>
+      <c r="E21" s="30" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="n"/>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
+      <c r="A22" s="26" t="n"/>
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="26" t="n"/>
+      <c r="E22" s="26" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="31" t="n"/>
-      <c r="C23" s="28" t="n"/>
-      <c r="D23" s="29" t="n"/>
-      <c r="E23" s="29" t="n"/>
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="29" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="n"/>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="24" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="25" t="n"/>
+      <c r="A24" s="26" t="n"/>
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="26" t="n"/>
+      <c r="E24" s="26" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="31" t="n"/>
-      <c r="C25" s="28" t="n"/>
-      <c r="D25" s="29" t="n"/>
-      <c r="E25" s="29" t="n"/>
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="29" t="n"/>
+      <c r="D25" s="30" t="n"/>
+      <c r="E25" s="30" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="n"/>
-      <c r="B26" s="27" t="n"/>
-      <c r="C26" s="24" t="n"/>
-      <c r="D26" s="25" t="n"/>
-      <c r="E26" s="25" t="n"/>
+      <c r="A26" s="26" t="n"/>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="25" t="n"/>
+      <c r="D26" s="26" t="n"/>
+      <c r="E26" s="26" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="28" t="n"/>
-      <c r="D27" s="29" t="n"/>
-      <c r="E27" s="29" t="n"/>
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="29" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="30" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="n"/>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="24" t="n"/>
-      <c r="D28" s="25" t="n"/>
-      <c r="E28" s="25" t="n"/>
+      <c r="A28" s="26" t="n"/>
+      <c r="B28" s="28" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="26" t="n"/>
+      <c r="E28" s="26" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="n"/>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="29" t="n"/>
-      <c r="E29" s="29" t="n"/>
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="32" t="n"/>
+      <c r="C29" s="29" t="n"/>
+      <c r="D29" s="30" t="n"/>
+      <c r="E29" s="30" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="n"/>
-      <c r="B30" s="27" t="n"/>
-      <c r="C30" s="24" t="n"/>
-      <c r="D30" s="25" t="n"/>
-      <c r="E30" s="25" t="n"/>
+      <c r="A30" s="26" t="n"/>
+      <c r="B30" s="28" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="26" t="n"/>
+      <c r="E30" s="26" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="31" t="n"/>
-      <c r="C31" s="28" t="n"/>
-      <c r="D31" s="29" t="n"/>
-      <c r="E31" s="29" t="n"/>
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="32" t="n"/>
+      <c r="C31" s="29" t="n"/>
+      <c r="D31" s="30" t="n"/>
+      <c r="E31" s="30" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="24" t="n"/>
-      <c r="D32" s="25" t="n"/>
-      <c r="E32" s="25" t="n"/>
+      <c r="A32" s="26" t="n"/>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="25" t="n"/>
+      <c r="D32" s="26" t="n"/>
+      <c r="E32" s="26" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="n"/>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="28" t="n"/>
-      <c r="D33" s="29" t="n"/>
-      <c r="E33" s="29" t="n"/>
+      <c r="A33" s="30" t="n"/>
+      <c r="B33" s="32" t="n"/>
+      <c r="C33" s="29" t="n"/>
+      <c r="D33" s="30" t="n"/>
+      <c r="E33" s="30" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="24" t="n"/>
-      <c r="D34" s="25" t="n"/>
-      <c r="E34" s="25" t="n"/>
+      <c r="A34" s="26" t="n"/>
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="25" t="n"/>
+      <c r="D34" s="26" t="n"/>
+      <c r="E34" s="26" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="n"/>
-      <c r="B35" s="31" t="n"/>
-      <c r="C35" s="28" t="n"/>
-      <c r="D35" s="29" t="n"/>
-      <c r="E35" s="29" t="n"/>
+      <c r="A35" s="30" t="n"/>
+      <c r="B35" s="32" t="n"/>
+      <c r="C35" s="29" t="n"/>
+      <c r="D35" s="30" t="n"/>
+      <c r="E35" s="30" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="n"/>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="24" t="n"/>
-      <c r="D36" s="25" t="n"/>
-      <c r="E36" s="25" t="n"/>
+      <c r="A36" s="26" t="n"/>
+      <c r="B36" s="28" t="n"/>
+      <c r="C36" s="25" t="n"/>
+      <c r="D36" s="26" t="n"/>
+      <c r="E36" s="26" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="n"/>
-      <c r="B37" s="31" t="n"/>
-      <c r="C37" s="28" t="n"/>
-      <c r="D37" s="29" t="n"/>
-      <c r="E37" s="29" t="n"/>
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="32" t="n"/>
+      <c r="C37" s="29" t="n"/>
+      <c r="D37" s="30" t="n"/>
+      <c r="E37" s="30" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="25" t="n"/>
-      <c r="B38" s="27" t="n"/>
-      <c r="C38" s="24" t="n"/>
-      <c r="D38" s="25" t="n"/>
-      <c r="E38" s="25" t="n"/>
+      <c r="A38" s="26" t="n"/>
+      <c r="B38" s="28" t="n"/>
+      <c r="C38" s="25" t="n"/>
+      <c r="D38" s="26" t="n"/>
+      <c r="E38" s="26" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="n"/>
-      <c r="B39" s="31" t="n"/>
-      <c r="C39" s="28" t="n"/>
-      <c r="D39" s="29" t="n"/>
-      <c r="E39" s="29" t="n"/>
+      <c r="A39" s="30" t="n"/>
+      <c r="B39" s="32" t="n"/>
+      <c r="C39" s="29" t="n"/>
+      <c r="D39" s="30" t="n"/>
+      <c r="E39" s="30" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="24" t="n"/>
-      <c r="D40" s="25" t="n"/>
-      <c r="E40" s="25" t="n"/>
+      <c r="A40" s="26" t="n"/>
+      <c r="B40" s="28" t="n"/>
+      <c r="C40" s="25" t="n"/>
+      <c r="D40" s="26" t="n"/>
+      <c r="E40" s="26" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="n"/>
-      <c r="B41" s="31" t="n"/>
-      <c r="C41" s="28" t="n"/>
-      <c r="D41" s="29" t="n"/>
-      <c r="E41" s="29" t="n"/>
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="32" t="n"/>
+      <c r="C41" s="29" t="n"/>
+      <c r="D41" s="30" t="n"/>
+      <c r="E41" s="30" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="n"/>
-      <c r="B42" s="27" t="n"/>
-      <c r="C42" s="24" t="n"/>
-      <c r="D42" s="25" t="n"/>
-      <c r="E42" s="25" t="n"/>
+      <c r="A42" s="26" t="n"/>
+      <c r="B42" s="28" t="n"/>
+      <c r="C42" s="25" t="n"/>
+      <c r="D42" s="26" t="n"/>
+      <c r="E42" s="26" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="n"/>
-      <c r="B43" s="31" t="n"/>
-      <c r="C43" s="28" t="n"/>
-      <c r="D43" s="29" t="n"/>
-      <c r="E43" s="29" t="n"/>
+      <c r="A43" s="30" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="29" t="n"/>
+      <c r="D43" s="30" t="n"/>
+      <c r="E43" s="30" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:E43"/>
@@ -95630,7 +95659,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>LABORATOIRE</t>
         </is>
@@ -95643,408 +95672,408 @@
       <c r="G1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Dates et heures au format JJ/MM/AAAA HH:MM. Le délai est calculé par l'outil.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Échantillon</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Laboratoire</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Prélèvement</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Envoi</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Réception</t>
         </is>
       </c>
-      <c r="F3" s="23" t="inlineStr">
+      <c r="F3" s="24" t="inlineStr">
         <is>
           <t>Résultat le</t>
         </is>
       </c>
-      <c r="G3" s="23" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>Résultat</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="27" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="32" t="n"/>
-      <c r="D4" s="32" t="n"/>
-      <c r="E4" s="32" t="n"/>
-      <c r="F4" s="32" t="n"/>
-      <c r="G4" s="27" t="n"/>
+      <c r="A4" s="28" t="n"/>
+      <c r="B4" s="26" t="n"/>
+      <c r="C4" s="33" t="n"/>
+      <c r="D4" s="33" t="n"/>
+      <c r="E4" s="33" t="n"/>
+      <c r="F4" s="33" t="n"/>
+      <c r="G4" s="28" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="31" t="n"/>
-      <c r="B5" s="29" t="n"/>
-      <c r="C5" s="33" t="n"/>
-      <c r="D5" s="33" t="n"/>
-      <c r="E5" s="33" t="n"/>
-      <c r="F5" s="33" t="n"/>
-      <c r="G5" s="31" t="n"/>
+      <c r="A5" s="32" t="n"/>
+      <c r="B5" s="30" t="n"/>
+      <c r="C5" s="34" t="n"/>
+      <c r="D5" s="34" t="n"/>
+      <c r="E5" s="34" t="n"/>
+      <c r="F5" s="34" t="n"/>
+      <c r="G5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="27" t="n"/>
-      <c r="B6" s="25" t="n"/>
-      <c r="C6" s="32" t="n"/>
-      <c r="D6" s="32" t="n"/>
-      <c r="E6" s="32" t="n"/>
-      <c r="F6" s="32" t="n"/>
-      <c r="G6" s="27" t="n"/>
+      <c r="A6" s="28" t="n"/>
+      <c r="B6" s="26" t="n"/>
+      <c r="C6" s="33" t="n"/>
+      <c r="D6" s="33" t="n"/>
+      <c r="E6" s="33" t="n"/>
+      <c r="F6" s="33" t="n"/>
+      <c r="G6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="31" t="n"/>
-      <c r="B7" s="29" t="n"/>
-      <c r="C7" s="33" t="n"/>
-      <c r="D7" s="33" t="n"/>
-      <c r="E7" s="33" t="n"/>
-      <c r="F7" s="33" t="n"/>
-      <c r="G7" s="31" t="n"/>
+      <c r="A7" s="32" t="n"/>
+      <c r="B7" s="30" t="n"/>
+      <c r="C7" s="34" t="n"/>
+      <c r="D7" s="34" t="n"/>
+      <c r="E7" s="34" t="n"/>
+      <c r="F7" s="34" t="n"/>
+      <c r="G7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="27" t="n"/>
-      <c r="B8" s="25" t="n"/>
-      <c r="C8" s="32" t="n"/>
-      <c r="D8" s="32" t="n"/>
-      <c r="E8" s="32" t="n"/>
-      <c r="F8" s="32" t="n"/>
-      <c r="G8" s="27" t="n"/>
+      <c r="A8" s="28" t="n"/>
+      <c r="B8" s="26" t="n"/>
+      <c r="C8" s="33" t="n"/>
+      <c r="D8" s="33" t="n"/>
+      <c r="E8" s="33" t="n"/>
+      <c r="F8" s="33" t="n"/>
+      <c r="G8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="31" t="n"/>
-      <c r="B9" s="29" t="n"/>
-      <c r="C9" s="33" t="n"/>
-      <c r="D9" s="33" t="n"/>
-      <c r="E9" s="33" t="n"/>
-      <c r="F9" s="33" t="n"/>
-      <c r="G9" s="31" t="n"/>
+      <c r="A9" s="32" t="n"/>
+      <c r="B9" s="30" t="n"/>
+      <c r="C9" s="34" t="n"/>
+      <c r="D9" s="34" t="n"/>
+      <c r="E9" s="34" t="n"/>
+      <c r="F9" s="34" t="n"/>
+      <c r="G9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="27" t="n"/>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="32" t="n"/>
-      <c r="D10" s="32" t="n"/>
-      <c r="E10" s="32" t="n"/>
-      <c r="F10" s="32" t="n"/>
-      <c r="G10" s="27" t="n"/>
+      <c r="A10" s="28" t="n"/>
+      <c r="B10" s="26" t="n"/>
+      <c r="C10" s="33" t="n"/>
+      <c r="D10" s="33" t="n"/>
+      <c r="E10" s="33" t="n"/>
+      <c r="F10" s="33" t="n"/>
+      <c r="G10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="31" t="n"/>
-      <c r="B11" s="29" t="n"/>
-      <c r="C11" s="33" t="n"/>
-      <c r="D11" s="33" t="n"/>
-      <c r="E11" s="33" t="n"/>
-      <c r="F11" s="33" t="n"/>
-      <c r="G11" s="31" t="n"/>
+      <c r="A11" s="32" t="n"/>
+      <c r="B11" s="30" t="n"/>
+      <c r="C11" s="34" t="n"/>
+      <c r="D11" s="34" t="n"/>
+      <c r="E11" s="34" t="n"/>
+      <c r="F11" s="34" t="n"/>
+      <c r="G11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="27" t="n"/>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="32" t="n"/>
-      <c r="D12" s="32" t="n"/>
-      <c r="E12" s="32" t="n"/>
-      <c r="F12" s="32" t="n"/>
-      <c r="G12" s="27" t="n"/>
+      <c r="A12" s="28" t="n"/>
+      <c r="B12" s="26" t="n"/>
+      <c r="C12" s="33" t="n"/>
+      <c r="D12" s="33" t="n"/>
+      <c r="E12" s="33" t="n"/>
+      <c r="F12" s="33" t="n"/>
+      <c r="G12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="31" t="n"/>
-      <c r="B13" s="29" t="n"/>
-      <c r="C13" s="33" t="n"/>
-      <c r="D13" s="33" t="n"/>
-      <c r="E13" s="33" t="n"/>
-      <c r="F13" s="33" t="n"/>
-      <c r="G13" s="31" t="n"/>
+      <c r="A13" s="32" t="n"/>
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="34" t="n"/>
+      <c r="D13" s="34" t="n"/>
+      <c r="E13" s="34" t="n"/>
+      <c r="F13" s="34" t="n"/>
+      <c r="G13" s="32" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="27" t="n"/>
-      <c r="B14" s="25" t="n"/>
-      <c r="C14" s="32" t="n"/>
-      <c r="D14" s="32" t="n"/>
-      <c r="E14" s="32" t="n"/>
-      <c r="F14" s="32" t="n"/>
-      <c r="G14" s="27" t="n"/>
+      <c r="A14" s="28" t="n"/>
+      <c r="B14" s="26" t="n"/>
+      <c r="C14" s="33" t="n"/>
+      <c r="D14" s="33" t="n"/>
+      <c r="E14" s="33" t="n"/>
+      <c r="F14" s="33" t="n"/>
+      <c r="G14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="31" t="n"/>
-      <c r="B15" s="29" t="n"/>
-      <c r="C15" s="33" t="n"/>
-      <c r="D15" s="33" t="n"/>
-      <c r="E15" s="33" t="n"/>
-      <c r="F15" s="33" t="n"/>
-      <c r="G15" s="31" t="n"/>
+      <c r="A15" s="32" t="n"/>
+      <c r="B15" s="30" t="n"/>
+      <c r="C15" s="34" t="n"/>
+      <c r="D15" s="34" t="n"/>
+      <c r="E15" s="34" t="n"/>
+      <c r="F15" s="34" t="n"/>
+      <c r="G15" s="32" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="27" t="n"/>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="32" t="n"/>
-      <c r="D16" s="32" t="n"/>
-      <c r="E16" s="32" t="n"/>
-      <c r="F16" s="32" t="n"/>
-      <c r="G16" s="27" t="n"/>
+      <c r="A16" s="28" t="n"/>
+      <c r="B16" s="26" t="n"/>
+      <c r="C16" s="33" t="n"/>
+      <c r="D16" s="33" t="n"/>
+      <c r="E16" s="33" t="n"/>
+      <c r="F16" s="33" t="n"/>
+      <c r="G16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="31" t="n"/>
-      <c r="B17" s="29" t="n"/>
-      <c r="C17" s="33" t="n"/>
-      <c r="D17" s="33" t="n"/>
-      <c r="E17" s="33" t="n"/>
-      <c r="F17" s="33" t="n"/>
-      <c r="G17" s="31" t="n"/>
+      <c r="A17" s="32" t="n"/>
+      <c r="B17" s="30" t="n"/>
+      <c r="C17" s="34" t="n"/>
+      <c r="D17" s="34" t="n"/>
+      <c r="E17" s="34" t="n"/>
+      <c r="F17" s="34" t="n"/>
+      <c r="G17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="27" t="n"/>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="32" t="n"/>
-      <c r="E18" s="32" t="n"/>
-      <c r="F18" s="32" t="n"/>
-      <c r="G18" s="27" t="n"/>
+      <c r="A18" s="28" t="n"/>
+      <c r="B18" s="26" t="n"/>
+      <c r="C18" s="33" t="n"/>
+      <c r="D18" s="33" t="n"/>
+      <c r="E18" s="33" t="n"/>
+      <c r="F18" s="33" t="n"/>
+      <c r="G18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="31" t="n"/>
-      <c r="B19" s="29" t="n"/>
-      <c r="C19" s="33" t="n"/>
-      <c r="D19" s="33" t="n"/>
-      <c r="E19" s="33" t="n"/>
-      <c r="F19" s="33" t="n"/>
-      <c r="G19" s="31" t="n"/>
+      <c r="A19" s="32" t="n"/>
+      <c r="B19" s="30" t="n"/>
+      <c r="C19" s="34" t="n"/>
+      <c r="D19" s="34" t="n"/>
+      <c r="E19" s="34" t="n"/>
+      <c r="F19" s="34" t="n"/>
+      <c r="G19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="27" t="n"/>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="32" t="n"/>
-      <c r="D20" s="32" t="n"/>
-      <c r="E20" s="32" t="n"/>
-      <c r="F20" s="32" t="n"/>
-      <c r="G20" s="27" t="n"/>
+      <c r="A20" s="28" t="n"/>
+      <c r="B20" s="26" t="n"/>
+      <c r="C20" s="33" t="n"/>
+      <c r="D20" s="33" t="n"/>
+      <c r="E20" s="33" t="n"/>
+      <c r="F20" s="33" t="n"/>
+      <c r="G20" s="28" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="31" t="n"/>
-      <c r="B21" s="29" t="n"/>
-      <c r="C21" s="33" t="n"/>
-      <c r="D21" s="33" t="n"/>
-      <c r="E21" s="33" t="n"/>
-      <c r="F21" s="33" t="n"/>
-      <c r="G21" s="31" t="n"/>
+      <c r="A21" s="32" t="n"/>
+      <c r="B21" s="30" t="n"/>
+      <c r="C21" s="34" t="n"/>
+      <c r="D21" s="34" t="n"/>
+      <c r="E21" s="34" t="n"/>
+      <c r="F21" s="34" t="n"/>
+      <c r="G21" s="32" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="27" t="n"/>
-      <c r="B22" s="25" t="n"/>
-      <c r="C22" s="32" t="n"/>
-      <c r="D22" s="32" t="n"/>
-      <c r="E22" s="32" t="n"/>
-      <c r="F22" s="32" t="n"/>
-      <c r="G22" s="27" t="n"/>
+      <c r="A22" s="28" t="n"/>
+      <c r="B22" s="26" t="n"/>
+      <c r="C22" s="33" t="n"/>
+      <c r="D22" s="33" t="n"/>
+      <c r="E22" s="33" t="n"/>
+      <c r="F22" s="33" t="n"/>
+      <c r="G22" s="28" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="31" t="n"/>
-      <c r="B23" s="29" t="n"/>
-      <c r="C23" s="33" t="n"/>
-      <c r="D23" s="33" t="n"/>
-      <c r="E23" s="33" t="n"/>
-      <c r="F23" s="33" t="n"/>
-      <c r="G23" s="31" t="n"/>
+      <c r="A23" s="32" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="34" t="n"/>
+      <c r="D23" s="34" t="n"/>
+      <c r="E23" s="34" t="n"/>
+      <c r="F23" s="34" t="n"/>
+      <c r="G23" s="32" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="27" t="n"/>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="32" t="n"/>
-      <c r="D24" s="32" t="n"/>
-      <c r="E24" s="32" t="n"/>
-      <c r="F24" s="32" t="n"/>
-      <c r="G24" s="27" t="n"/>
+      <c r="A24" s="28" t="n"/>
+      <c r="B24" s="26" t="n"/>
+      <c r="C24" s="33" t="n"/>
+      <c r="D24" s="33" t="n"/>
+      <c r="E24" s="33" t="n"/>
+      <c r="F24" s="33" t="n"/>
+      <c r="G24" s="28" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="31" t="n"/>
-      <c r="B25" s="29" t="n"/>
-      <c r="C25" s="33" t="n"/>
-      <c r="D25" s="33" t="n"/>
-      <c r="E25" s="33" t="n"/>
-      <c r="F25" s="33" t="n"/>
-      <c r="G25" s="31" t="n"/>
+      <c r="A25" s="32" t="n"/>
+      <c r="B25" s="30" t="n"/>
+      <c r="C25" s="34" t="n"/>
+      <c r="D25" s="34" t="n"/>
+      <c r="E25" s="34" t="n"/>
+      <c r="F25" s="34" t="n"/>
+      <c r="G25" s="32" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="27" t="n"/>
-      <c r="B26" s="25" t="n"/>
-      <c r="C26" s="32" t="n"/>
-      <c r="D26" s="32" t="n"/>
-      <c r="E26" s="32" t="n"/>
-      <c r="F26" s="32" t="n"/>
-      <c r="G26" s="27" t="n"/>
+      <c r="A26" s="28" t="n"/>
+      <c r="B26" s="26" t="n"/>
+      <c r="C26" s="33" t="n"/>
+      <c r="D26" s="33" t="n"/>
+      <c r="E26" s="33" t="n"/>
+      <c r="F26" s="33" t="n"/>
+      <c r="G26" s="28" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="31" t="n"/>
-      <c r="B27" s="29" t="n"/>
-      <c r="C27" s="33" t="n"/>
-      <c r="D27" s="33" t="n"/>
-      <c r="E27" s="33" t="n"/>
-      <c r="F27" s="33" t="n"/>
-      <c r="G27" s="31" t="n"/>
+      <c r="A27" s="32" t="n"/>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="34" t="n"/>
+      <c r="D27" s="34" t="n"/>
+      <c r="E27" s="34" t="n"/>
+      <c r="F27" s="34" t="n"/>
+      <c r="G27" s="32" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="27" t="n"/>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="32" t="n"/>
-      <c r="D28" s="32" t="n"/>
-      <c r="E28" s="32" t="n"/>
-      <c r="F28" s="32" t="n"/>
-      <c r="G28" s="27" t="n"/>
+      <c r="A28" s="28" t="n"/>
+      <c r="B28" s="26" t="n"/>
+      <c r="C28" s="33" t="n"/>
+      <c r="D28" s="33" t="n"/>
+      <c r="E28" s="33" t="n"/>
+      <c r="F28" s="33" t="n"/>
+      <c r="G28" s="28" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="31" t="n"/>
-      <c r="B29" s="29" t="n"/>
-      <c r="C29" s="33" t="n"/>
-      <c r="D29" s="33" t="n"/>
-      <c r="E29" s="33" t="n"/>
-      <c r="F29" s="33" t="n"/>
-      <c r="G29" s="31" t="n"/>
+      <c r="A29" s="32" t="n"/>
+      <c r="B29" s="30" t="n"/>
+      <c r="C29" s="34" t="n"/>
+      <c r="D29" s="34" t="n"/>
+      <c r="E29" s="34" t="n"/>
+      <c r="F29" s="34" t="n"/>
+      <c r="G29" s="32" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="27" t="n"/>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="32" t="n"/>
-      <c r="D30" s="32" t="n"/>
-      <c r="E30" s="32" t="n"/>
-      <c r="F30" s="32" t="n"/>
-      <c r="G30" s="27" t="n"/>
+      <c r="A30" s="28" t="n"/>
+      <c r="B30" s="26" t="n"/>
+      <c r="C30" s="33" t="n"/>
+      <c r="D30" s="33" t="n"/>
+      <c r="E30" s="33" t="n"/>
+      <c r="F30" s="33" t="n"/>
+      <c r="G30" s="28" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="31" t="n"/>
-      <c r="B31" s="29" t="n"/>
-      <c r="C31" s="33" t="n"/>
-      <c r="D31" s="33" t="n"/>
-      <c r="E31" s="33" t="n"/>
-      <c r="F31" s="33" t="n"/>
-      <c r="G31" s="31" t="n"/>
+      <c r="A31" s="32" t="n"/>
+      <c r="B31" s="30" t="n"/>
+      <c r="C31" s="34" t="n"/>
+      <c r="D31" s="34" t="n"/>
+      <c r="E31" s="34" t="n"/>
+      <c r="F31" s="34" t="n"/>
+      <c r="G31" s="32" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="27" t="n"/>
-      <c r="B32" s="25" t="n"/>
-      <c r="C32" s="32" t="n"/>
-      <c r="D32" s="32" t="n"/>
-      <c r="E32" s="32" t="n"/>
-      <c r="F32" s="32" t="n"/>
-      <c r="G32" s="27" t="n"/>
+      <c r="A32" s="28" t="n"/>
+      <c r="B32" s="26" t="n"/>
+      <c r="C32" s="33" t="n"/>
+      <c r="D32" s="33" t="n"/>
+      <c r="E32" s="33" t="n"/>
+      <c r="F32" s="33" t="n"/>
+      <c r="G32" s="28" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="31" t="n"/>
-      <c r="B33" s="29" t="n"/>
-      <c r="C33" s="33" t="n"/>
-      <c r="D33" s="33" t="n"/>
-      <c r="E33" s="33" t="n"/>
-      <c r="F33" s="33" t="n"/>
-      <c r="G33" s="31" t="n"/>
+      <c r="A33" s="32" t="n"/>
+      <c r="B33" s="30" t="n"/>
+      <c r="C33" s="34" t="n"/>
+      <c r="D33" s="34" t="n"/>
+      <c r="E33" s="34" t="n"/>
+      <c r="F33" s="34" t="n"/>
+      <c r="G33" s="32" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="27" t="n"/>
-      <c r="B34" s="25" t="n"/>
-      <c r="C34" s="32" t="n"/>
-      <c r="D34" s="32" t="n"/>
-      <c r="E34" s="32" t="n"/>
-      <c r="F34" s="32" t="n"/>
-      <c r="G34" s="27" t="n"/>
+      <c r="A34" s="28" t="n"/>
+      <c r="B34" s="26" t="n"/>
+      <c r="C34" s="33" t="n"/>
+      <c r="D34" s="33" t="n"/>
+      <c r="E34" s="33" t="n"/>
+      <c r="F34" s="33" t="n"/>
+      <c r="G34" s="28" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="31" t="n"/>
-      <c r="B35" s="29" t="n"/>
-      <c r="C35" s="33" t="n"/>
-      <c r="D35" s="33" t="n"/>
-      <c r="E35" s="33" t="n"/>
-      <c r="F35" s="33" t="n"/>
-      <c r="G35" s="31" t="n"/>
+      <c r="A35" s="32" t="n"/>
+      <c r="B35" s="30" t="n"/>
+      <c r="C35" s="34" t="n"/>
+      <c r="D35" s="34" t="n"/>
+      <c r="E35" s="34" t="n"/>
+      <c r="F35" s="34" t="n"/>
+      <c r="G35" s="32" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="27" t="n"/>
-      <c r="B36" s="25" t="n"/>
-      <c r="C36" s="32" t="n"/>
-      <c r="D36" s="32" t="n"/>
-      <c r="E36" s="32" t="n"/>
-      <c r="F36" s="32" t="n"/>
-      <c r="G36" s="27" t="n"/>
+      <c r="A36" s="28" t="n"/>
+      <c r="B36" s="26" t="n"/>
+      <c r="C36" s="33" t="n"/>
+      <c r="D36" s="33" t="n"/>
+      <c r="E36" s="33" t="n"/>
+      <c r="F36" s="33" t="n"/>
+      <c r="G36" s="28" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="31" t="n"/>
-      <c r="B37" s="29" t="n"/>
-      <c r="C37" s="33" t="n"/>
-      <c r="D37" s="33" t="n"/>
-      <c r="E37" s="33" t="n"/>
-      <c r="F37" s="33" t="n"/>
-      <c r="G37" s="31" t="n"/>
+      <c r="A37" s="32" t="n"/>
+      <c r="B37" s="30" t="n"/>
+      <c r="C37" s="34" t="n"/>
+      <c r="D37" s="34" t="n"/>
+      <c r="E37" s="34" t="n"/>
+      <c r="F37" s="34" t="n"/>
+      <c r="G37" s="32" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="27" t="n"/>
-      <c r="B38" s="25" t="n"/>
-      <c r="C38" s="32" t="n"/>
-      <c r="D38" s="32" t="n"/>
-      <c r="E38" s="32" t="n"/>
-      <c r="F38" s="32" t="n"/>
-      <c r="G38" s="27" t="n"/>
+      <c r="A38" s="28" t="n"/>
+      <c r="B38" s="26" t="n"/>
+      <c r="C38" s="33" t="n"/>
+      <c r="D38" s="33" t="n"/>
+      <c r="E38" s="33" t="n"/>
+      <c r="F38" s="33" t="n"/>
+      <c r="G38" s="28" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="31" t="n"/>
-      <c r="B39" s="29" t="n"/>
-      <c r="C39" s="33" t="n"/>
-      <c r="D39" s="33" t="n"/>
-      <c r="E39" s="33" t="n"/>
-      <c r="F39" s="33" t="n"/>
-      <c r="G39" s="31" t="n"/>
+      <c r="A39" s="32" t="n"/>
+      <c r="B39" s="30" t="n"/>
+      <c r="C39" s="34" t="n"/>
+      <c r="D39" s="34" t="n"/>
+      <c r="E39" s="34" t="n"/>
+      <c r="F39" s="34" t="n"/>
+      <c r="G39" s="32" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="27" t="n"/>
-      <c r="B40" s="25" t="n"/>
-      <c r="C40" s="32" t="n"/>
-      <c r="D40" s="32" t="n"/>
-      <c r="E40" s="32" t="n"/>
-      <c r="F40" s="32" t="n"/>
-      <c r="G40" s="27" t="n"/>
+      <c r="A40" s="28" t="n"/>
+      <c r="B40" s="26" t="n"/>
+      <c r="C40" s="33" t="n"/>
+      <c r="D40" s="33" t="n"/>
+      <c r="E40" s="33" t="n"/>
+      <c r="F40" s="33" t="n"/>
+      <c r="G40" s="28" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="31" t="n"/>
-      <c r="B41" s="29" t="n"/>
-      <c r="C41" s="33" t="n"/>
-      <c r="D41" s="33" t="n"/>
-      <c r="E41" s="33" t="n"/>
-      <c r="F41" s="33" t="n"/>
-      <c r="G41" s="31" t="n"/>
+      <c r="A41" s="32" t="n"/>
+      <c r="B41" s="30" t="n"/>
+      <c r="C41" s="34" t="n"/>
+      <c r="D41" s="34" t="n"/>
+      <c r="E41" s="34" t="n"/>
+      <c r="F41" s="34" t="n"/>
+      <c r="G41" s="32" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="27" t="n"/>
-      <c r="B42" s="25" t="n"/>
-      <c r="C42" s="32" t="n"/>
-      <c r="D42" s="32" t="n"/>
-      <c r="E42" s="32" t="n"/>
-      <c r="F42" s="32" t="n"/>
-      <c r="G42" s="27" t="n"/>
+      <c r="A42" s="28" t="n"/>
+      <c r="B42" s="26" t="n"/>
+      <c r="C42" s="33" t="n"/>
+      <c r="D42" s="33" t="n"/>
+      <c r="E42" s="33" t="n"/>
+      <c r="F42" s="33" t="n"/>
+      <c r="G42" s="28" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="31" t="n"/>
-      <c r="B43" s="29" t="n"/>
-      <c r="C43" s="33" t="n"/>
-      <c r="D43" s="33" t="n"/>
-      <c r="E43" s="33" t="n"/>
-      <c r="F43" s="33" t="n"/>
-      <c r="G43" s="31" t="n"/>
+      <c r="A43" s="32" t="n"/>
+      <c r="B43" s="30" t="n"/>
+      <c r="C43" s="34" t="n"/>
+      <c r="D43" s="34" t="n"/>
+      <c r="E43" s="34" t="n"/>
+      <c r="F43" s="34" t="n"/>
+      <c r="G43" s="32" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:G43"/>
@@ -96083,7 +96112,7 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="12" t="inlineStr">
+      <c r="A1" s="13" t="inlineStr">
         <is>
           <t>ACTIONS IMMÉDIATES</t>
         </is>
@@ -96094,318 +96123,318 @@
       <c r="E1" s="1" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="13" t="inlineStr">
+      <c r="A2" s="14" t="inlineStr">
         <is>
           <t>Vide = l'outil propose des actions automatiquement.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="34" customHeight="1">
-      <c r="A3" s="23" t="inlineStr">
+      <c r="A3" s="24" t="inlineStr">
         <is>
           <t>Action</t>
         </is>
       </c>
-      <c r="B3" s="23" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>Priorité</t>
         </is>
       </c>
-      <c r="C3" s="23" t="inlineStr">
+      <c r="C3" s="24" t="inlineStr">
         <is>
           <t>Responsable</t>
         </is>
       </c>
-      <c r="D3" s="23" t="inlineStr">
+      <c r="D3" s="24" t="inlineStr">
         <is>
           <t>Échéance</t>
         </is>
       </c>
-      <c r="E3" s="23" t="inlineStr">
+      <c r="E3" s="24" t="inlineStr">
         <is>
           <t>Statut</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="n"/>
-      <c r="B4" s="27" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="24" t="n"/>
-      <c r="E4" s="27" t="n"/>
+      <c r="A4" s="26" t="n"/>
+      <c r="B4" s="28" t="n"/>
+      <c r="C4" s="26" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="28" t="n"/>
     </row>
     <row r="5">
-      <c r="A5" s="29" t="n"/>
-      <c r="B5" s="31" t="n"/>
-      <c r="C5" s="29" t="n"/>
-      <c r="D5" s="28" t="n"/>
-      <c r="E5" s="31" t="n"/>
+      <c r="A5" s="30" t="n"/>
+      <c r="B5" s="32" t="n"/>
+      <c r="C5" s="30" t="n"/>
+      <c r="D5" s="29" t="n"/>
+      <c r="E5" s="32" t="n"/>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="27" t="n"/>
-      <c r="C6" s="25" t="n"/>
-      <c r="D6" s="24" t="n"/>
-      <c r="E6" s="27" t="n"/>
+      <c r="A6" s="26" t="n"/>
+      <c r="B6" s="28" t="n"/>
+      <c r="C6" s="26" t="n"/>
+      <c r="D6" s="25" t="n"/>
+      <c r="E6" s="28" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="29" t="n"/>
-      <c r="B7" s="31" t="n"/>
-      <c r="C7" s="29" t="n"/>
-      <c r="D7" s="28" t="n"/>
-      <c r="E7" s="31" t="n"/>
+      <c r="A7" s="30" t="n"/>
+      <c r="B7" s="32" t="n"/>
+      <c r="C7" s="30" t="n"/>
+      <c r="D7" s="29" t="n"/>
+      <c r="E7" s="32" t="n"/>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="n"/>
-      <c r="B8" s="27" t="n"/>
-      <c r="C8" s="25" t="n"/>
-      <c r="D8" s="24" t="n"/>
-      <c r="E8" s="27" t="n"/>
+      <c r="A8" s="26" t="n"/>
+      <c r="B8" s="28" t="n"/>
+      <c r="C8" s="26" t="n"/>
+      <c r="D8" s="25" t="n"/>
+      <c r="E8" s="28" t="n"/>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n"/>
-      <c r="B9" s="31" t="n"/>
-      <c r="C9" s="29" t="n"/>
-      <c r="D9" s="28" t="n"/>
-      <c r="E9" s="31" t="n"/>
+      <c r="A9" s="30" t="n"/>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="30" t="n"/>
+      <c r="D9" s="29" t="n"/>
+      <c r="E9" s="32" t="n"/>
     </row>
     <row r="10">
-      <c r="A10" s="25" t="n"/>
-      <c r="B10" s="27" t="n"/>
-      <c r="C10" s="25" t="n"/>
-      <c r="D10" s="24" t="n"/>
-      <c r="E10" s="27" t="n"/>
+      <c r="A10" s="26" t="n"/>
+      <c r="B10" s="28" t="n"/>
+      <c r="C10" s="26" t="n"/>
+      <c r="D10" s="25" t="n"/>
+      <c r="E10" s="28" t="n"/>
     </row>
     <row r="11">
-      <c r="A11" s="29" t="n"/>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="29" t="n"/>
-      <c r="D11" s="28" t="n"/>
-      <c r="E11" s="31" t="n"/>
+      <c r="A11" s="30" t="n"/>
+      <c r="B11" s="32" t="n"/>
+      <c r="C11" s="30" t="n"/>
+      <c r="D11" s="29" t="n"/>
+      <c r="E11" s="32" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="27" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="24" t="n"/>
-      <c r="E12" s="27" t="n"/>
+      <c r="A12" s="26" t="n"/>
+      <c r="B12" s="28" t="n"/>
+      <c r="C12" s="26" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="28" t="n"/>
     </row>
     <row r="13">
-      <c r="A13" s="29" t="n"/>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="29" t="n"/>
-      <c r="D13" s="28" t="n"/>
-      <c r="E13" s="31" t="n"/>
+      <c r="A13" s="30" t="n"/>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="29" t="n"/>
+      <c r="E13" s="32" t="n"/>
     </row>
     <row r="14">
-      <c r="A14" s="25" t="n"/>
-      <c r="B14" s="27" t="n"/>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="24" t="n"/>
-      <c r="E14" s="27" t="n"/>
+      <c r="A14" s="26" t="n"/>
+      <c r="B14" s="28" t="n"/>
+      <c r="C14" s="26" t="n"/>
+      <c r="D14" s="25" t="n"/>
+      <c r="E14" s="28" t="n"/>
     </row>
     <row r="15">
-      <c r="A15" s="29" t="n"/>
-      <c r="B15" s="31" t="n"/>
-      <c r="C15" s="29" t="n"/>
-      <c r="D15" s="28" t="n"/>
-      <c r="E15" s="31" t="n"/>
+      <c r="A15" s="30" t="n"/>
+      <c r="B15" s="32" t="n"/>
+      <c r="C15" s="30" t="n"/>
+      <c r="D15" s="29" t="n"/>
+      <c r="E15" s="32" t="n"/>
     </row>
     <row r="16">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="27" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="24" t="n"/>
-      <c r="E16" s="27" t="n"/>
+      <c r="A16" s="26" t="n"/>
+      <c r="B16" s="28" t="n"/>
+      <c r="C16" s="26" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="28" t="n"/>
     </row>
     <row r="17">
-      <c r="A17" s="29" t="n"/>
-      <c r="B17" s="31" t="n"/>
-      <c r="C17" s="29" t="n"/>
-      <c r="D17" s="28" t="n"/>
-      <c r="E17" s="31" t="n"/>
+      <c r="A17" s="30" t="n"/>
+      <c r="B17" s="32" t="n"/>
+      <c r="C17" s="30" t="n"/>
+      <c r="D17" s="29" t="n"/>
+      <c r="E17" s="32" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="27" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="24" t="n"/>
-      <c r="E18" s="27" t="n"/>
+      <c r="A18" s="26" t="n"/>
+      <c r="B18" s="28" t="n"/>
+      <c r="C18" s="26" t="n"/>
+      <c r="D18" s="25" t="n"/>
+      <c r="E18" s="28" t="n"/>
     </row>
     <row r="19">
-      <c r="A19" s="29" t="n"/>
-      <c r="B19" s="31" t="n"/>
-      <c r="C19" s="29" t="n"/>
-      <c r="D19" s="28" t="n"/>
-      <c r="E19" s="31" t="n"/>
+      <c r="A19" s="30" t="n"/>
+      <c r="B19" s="32" t="n"/>
+      <c r="C19" s="30" t="n"/>
+      <c r="D19" s="29" t="n"/>
+      <c r="E19" s="32" t="n"/>
     </row>
     <row r="20">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="27" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="24" t="n"/>
-      <c r="E20" s="27" t="n"/>
+      <c r="A20" s="26" t="n"/>
+      <c r="B20" s="28" t="n"/>
+      <c r="C20" s="26" t="n"/>
+      <c r="D20" s="25" t="n"/>
+      <c r="E20" s="28" t="n"/>
     </row>
     <row r="21">
-      <c r="A21" s="29" t="n"/>
-      <c r="B21" s="31" t="n"/>
-      <c r="C21" s="29" t="n"/>
-      <c r="D21" s="28" t="n"/>
-      <c r="E21" s="31" t="n"/>
+      <c r="A21" s="30" t="n"/>
+      <c r="B21" s="32" t="n"/>
+      <c r="C21" s="30" t="n"/>
+      <c r="D21" s="29" t="n"/>
+      <c r="E21" s="32" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="25" t="n"/>
-      <c r="B22" s="27" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="24" t="n"/>
-      <c r="E22" s="27" t="n"/>
+      <c r="A22" s="26" t="n"/>
+      <c r="B22" s="28" t="n"/>
+      <c r="C22" s="26" t="n"/>
+      <c r="D22" s="25" t="n"/>
+      <c r="E22" s="28" t="n"/>
     </row>
     <row r="23">
-      <c r="A23" s="29" t="n"/>
-      <c r="B23" s="31" t="n"/>
-      <c r="C23" s="29" t="n"/>
-      <c r="D23" s="28" t="n"/>
-      <c r="E23" s="31" t="n"/>
+      <c r="A23" s="30" t="n"/>
+      <c r="B23" s="32" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="29" t="n"/>
+      <c r="E23" s="32" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="25" t="n"/>
-      <c r="B24" s="27" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="24" t="n"/>
-      <c r="E24" s="27" t="n"/>
+      <c r="A24" s="26" t="n"/>
+      <c r="B24" s="28" t="n"/>
+      <c r="C24" s="26" t="n"/>
+      <c r="D24" s="25" t="n"/>
+      <c r="E24" s="28" t="n"/>
     </row>
     <row r="25">
-      <c r="A25" s="29" t="n"/>
-      <c r="B25" s="31" t="n"/>
-      <c r="C25" s="29" t="n"/>
-      <c r="D25" s="28" t="n"/>
-      <c r="E25" s="31" t="n"/>
+      <c r="A25" s="30" t="n"/>
+      <c r="B25" s="32" t="n"/>
+      <c r="C25" s="30" t="n"/>
+      <c r="D25" s="29" t="n"/>
+      <c r="E25" s="32" t="n"/>
     </row>
     <row r="26">
-      <c r="A26" s="25" t="n"/>
-      <c r="B26" s="27" t="n"/>
-      <c r="C26" s="25" t="n"/>
-      <c r="D26" s="24" t="n"/>
-      <c r="E26" s="27" t="n"/>
+      <c r="A26" s="26" t="n"/>
+      <c r="B26" s="28" t="n"/>
+      <c r="C26" s="26" t="n"/>
+      <c r="D26" s="25" t="n"/>
+      <c r="E26" s="28" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="29" t="n"/>
-      <c r="B27" s="31" t="n"/>
-      <c r="C27" s="29" t="n"/>
-      <c r="D27" s="28" t="n"/>
-      <c r="E27" s="31" t="n"/>
+      <c r="A27" s="30" t="n"/>
+      <c r="B27" s="32" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="29" t="n"/>
+      <c r="E27" s="32" t="n"/>
     </row>
     <row r="28">
-      <c r="A28" s="25" t="n"/>
-      <c r="B28" s="27" t="n"/>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="24" t="n"/>
-      <c r="E28" s="27" t="n"/>
+      <c r="A28" s="26" t="n"/>
+      <c r="B28" s="28" t="n"/>
+      <c r="C28" s="26" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="28" t="n"/>
     </row>
     <row r="29">
-      <c r="A29" s="29" t="n"/>
-      <c r="B29" s="31" t="n"/>
-      <c r="C29" s="29" t="n"/>
-      <c r="D29" s="28" t="n"/>
-      <c r="E29" s="31" t="n"/>
+      <c r="A29" s="30" t="n"/>
+      <c r="B29" s="32" t="n"/>
+      <c r="C29" s="30" t="n"/>
+      <c r="D29" s="29" t="n"/>
+      <c r="E29" s="32" t="n"/>
     </row>
     <row r="30">
-      <c r="A30" s="25" t="n"/>
-      <c r="B30" s="27" t="n"/>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="24" t="n"/>
-      <c r="E30" s="27" t="n"/>
+      <c r="A30" s="26" t="n"/>
+      <c r="B30" s="28" t="n"/>
+      <c r="C30" s="26" t="n"/>
+      <c r="D30" s="25" t="n"/>
+      <c r="E30" s="28" t="n"/>
     </row>
     <row r="31">
-      <c r="A31" s="29" t="n"/>
-      <c r="B31" s="31" t="n"/>
-      <c r="C31" s="29" t="n"/>
-      <c r="D31" s="28" t="n"/>
-      <c r="E31" s="31" t="n"/>
+      <c r="A31" s="30" t="n"/>
+      <c r="B31" s="32" t="n"/>
+      <c r="C31" s="30" t="n"/>
+      <c r="D31" s="29" t="n"/>
+      <c r="E31" s="32" t="n"/>
     </row>
     <row r="32">
-      <c r="A32" s="25" t="n"/>
-      <c r="B32" s="27" t="n"/>
-      <c r="C32" s="25" t="n"/>
-      <c r="D32" s="24" t="n"/>
-      <c r="E32" s="27" t="n"/>
+      <c r="A32" s="26" t="n"/>
+      <c r="B32" s="28" t="n"/>
+      <c r="C32" s="26" t="n"/>
+      <c r="D32" s="25" t="n"/>
+      <c r="E32" s="28" t="n"/>
     </row>
     <row r="33">
-      <c r="A33" s="29" t="n"/>
-      <c r="B33" s="31" t="n"/>
-      <c r="C33" s="29" t="n"/>
-      <c r="D33" s="28" t="n"/>
-      <c r="E33" s="31" t="n"/>
+      <c r="A33" s="30" t="n"/>
+      <c r="B33" s="32" t="n"/>
+      <c r="C33" s="30" t="n"/>
+      <c r="D33" s="29" t="n"/>
+      <c r="E33" s="32" t="n"/>
     </row>
     <row r="34">
-      <c r="A34" s="25" t="n"/>
-      <c r="B34" s="27" t="n"/>
-      <c r="C34" s="25" t="n"/>
-      <c r="D34" s="24" t="n"/>
-      <c r="E34" s="27" t="n"/>
+      <c r="A34" s="26" t="n"/>
+      <c r="B34" s="28" t="n"/>
+      <c r="C34" s="26" t="n"/>
+      <c r="D34" s="25" t="n"/>
+      <c r="E34" s="28" t="n"/>
     </row>
     <row r="35">
-      <c r="A35" s="29" t="n"/>
-      <c r="B35" s="31" t="n"/>
-      <c r="C35" s="29" t="n"/>
-      <c r="D35" s="28" t="n"/>
-      <c r="E35" s="31" t="n"/>
+      <c r="A35" s="30" t="n"/>
+      <c r="B35" s="32" t="n"/>
+      <c r="C35" s="30" t="n"/>
+      <c r="D35" s="29" t="n"/>
+      <c r="E35" s="32" t="n"/>
     </row>
     <row r="36">
-      <c r="A36" s="25" t="n"/>
-      <c r="B36" s="27" t="n"/>
-      <c r="C36" s="25" t="n"/>
-      <c r="D36" s="24" t="n"/>
-      <c r="E36" s="27" t="n"/>
+      <c r="A36" s="26" t="n"/>
+      <c r="B36" s="28" t="n"/>
+      <c r="C36" s="26" t="n"/>
+      <c r="D36" s="25" t="n"/>
+      <c r="E36" s="28" t="n"/>
     </row>
     <row r="37">
-      <c r="A37" s="29" t="n"/>
-      <c r="B37" s="31" t="n"/>
-      <c r="C37" s="29" t="n"/>
-      <c r="D37" s="28" t="n"/>
-      <c r="E37" s="31" t="n"/>
+      <c r="A37" s="30" t="n"/>
+      <c r="B37" s="32" t="n"/>
+      <c r="C37" s="30" t="n"/>
+      <c r="D37" s="29" t="n"/>
+      <c r="E37" s="32" t="n"/>
     </row>
     <row r="38">
-      <c r="A38" s="25" t="n"/>
-      <c r="B38" s="27" t="n"/>
-      <c r="C38" s="25" t="n"/>
-      <c r="D38" s="24" t="n"/>
-      <c r="E38" s="27" t="n"/>
+      <c r="A38" s="26" t="n"/>
+      <c r="B38" s="28" t="n"/>
+      <c r="C38" s="26" t="n"/>
+      <c r="D38" s="25" t="n"/>
+      <c r="E38" s="28" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="29" t="n"/>
-      <c r="B39" s="31" t="n"/>
-      <c r="C39" s="29" t="n"/>
-      <c r="D39" s="28" t="n"/>
-      <c r="E39" s="31" t="n"/>
+      <c r="A39" s="30" t="n"/>
+      <c r="B39" s="32" t="n"/>
+      <c r="C39" s="30" t="n"/>
+      <c r="D39" s="29" t="n"/>
+      <c r="E39" s="32" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="25" t="n"/>
-      <c r="B40" s="27" t="n"/>
-      <c r="C40" s="25" t="n"/>
-      <c r="D40" s="24" t="n"/>
-      <c r="E40" s="27" t="n"/>
+      <c r="A40" s="26" t="n"/>
+      <c r="B40" s="28" t="n"/>
+      <c r="C40" s="26" t="n"/>
+      <c r="D40" s="25" t="n"/>
+      <c r="E40" s="28" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="29" t="n"/>
-      <c r="B41" s="31" t="n"/>
-      <c r="C41" s="29" t="n"/>
-      <c r="D41" s="28" t="n"/>
-      <c r="E41" s="31" t="n"/>
+      <c r="A41" s="30" t="n"/>
+      <c r="B41" s="32" t="n"/>
+      <c r="C41" s="30" t="n"/>
+      <c r="D41" s="29" t="n"/>
+      <c r="E41" s="32" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="25" t="n"/>
-      <c r="B42" s="27" t="n"/>
-      <c r="C42" s="25" t="n"/>
-      <c r="D42" s="24" t="n"/>
-      <c r="E42" s="27" t="n"/>
+      <c r="A42" s="26" t="n"/>
+      <c r="B42" s="28" t="n"/>
+      <c r="C42" s="26" t="n"/>
+      <c r="D42" s="25" t="n"/>
+      <c r="E42" s="28" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="29" t="n"/>
-      <c r="B43" s="31" t="n"/>
-      <c r="C43" s="29" t="n"/>
-      <c r="D43" s="28" t="n"/>
-      <c r="E43" s="31" t="n"/>
+      <c r="A43" s="30" t="n"/>
+      <c r="B43" s="32" t="n"/>
+      <c r="C43" s="30" t="n"/>
+      <c r="D43" s="29" t="n"/>
+      <c r="E43" s="32" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A3:E43"/>
